--- a/reports/tool_chat/report.xlsx
+++ b/reports/tool_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="160">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc5a-133d-7d70-a7a8-c7574189a3b7</t>
+    <t>01a0cce3-7c59-7500-9bb3-9e974c30762a</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc5a-1346-7611-99e8-b4878ab9ac1b</t>
+    <t>01a0cce3-7c62-7600-b525-c91ab3e30b57</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -342,8 +342,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_N3tIiLfCsL87adnZuJLU4z1t", "id": "fc_05e0c4a49feda864006ab34a4330b887d285a8810bf7fb41b0", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_N3tIiLfCsL87adnZuJLU4z1t", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_aqkxBJdFbfYxEHqTsjw3OgFh", "id": "fc_08d6966ad3cb0e2d006ab36d70b7f487d28768709fe626665a", "index": 0}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_aqkxBJdFbfYxEHqTsjw3OgFh", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,7 +355,7 @@
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0cc5a-178b-7961-af54-0594e2d118f3</t>
+    <t>01a0cce3-814f-7662-9b6a-9b765682d148</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -373,7 +373,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc5a-1793-7632-878e-7d9f6b57f0d0</t>
+    <t>01a0cce3-8153-7ff3-bd84-ba4dd62a9af7</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -382,7 +382,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Your input was: ReAct", "phase": "final_answer", "index": 0, "id": "msg_05e0c4a49feda864006ab34a44c25487d2986301b1ec0f3385"}]</t>
+    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_08d6966ad3cb0e2d006ab36d71e44487d293994b9490428e9d"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -391,20 +391,17 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cc5a-1dc7-7672-aca2-7611626ff48f</t>
+    <t>01a0cce3-8641-7331-a98e-1aa32356ee5c</t>
   </si>
   <si>
     <t>Echo this text: Tool observations</t>
   </si>
   <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_05e0c4a49feda864006ab34a46cc4487d28e566ce19612d6d1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0pGzD0rG6YkanBRpjuU_8pNDlVfJ6tyxsRvdtMzNZD5WuwkY9-qPg8JQ8XlTOpONBOPbN9t2VRAvaYc1Jd4YSg3Dxzfh4EfIZn3dAYjPAtZftNA_wH9RDGqYkGttCDqCWLkwzE4viYRXi12qTEDeAN7QhWOPpwJ1_55vEvaLV9L2-gGzqPAe2YXvXcv0wuQvXDtVRKSiB-FGaClpSGaJCu9SAW9UVBckgm-KFd8bd1qTWiVeSuglomDv8OdAAaOs9jdzbQRUAFe_x7MK5AEj4zqGZl5_sWR2pK5hRP8NCrWeGwB7Saj6cS0pK0_RWAkXQRh8HL7uDbbkVHBItnAu_XwydIB_xmq2zQTpYtabN9vsxzwObq5i-t5lHRcoVAqpFx8Eb-bXsLGk6qquU-J10xMpQGK2Sip8PrcNiAYdRVbhDjZtfrqTcMG7gykF4p-pEqkn8dFcs2ieEeBvTbGTg2UXLL0rkG3L5QnOsi9RoQJ967zBs26tcAdLjPr-WusYaTTTQgsMKpHl1o_j_EDAeVCnKYef2I_6bfzgZGnhbXOsAgfiEjbEljF-BIZBO-Mcr6oulZk7JtJhQDrytgP4DnvsOTz5jYDVpP2o2TG9V5NYVjafdyIhyjjwiW4J1c1IW3-2QJ1hBKw0ReWLpe8XrAYZKR2W8iQBUSW3NSjs09yclB7xiq9DtMN3kWCkfrOfOPUQY3Sq8cd4kPhNth9KhzLApDdJLgTaMjcJdECuvzenp3-2PlkiPrgHxuOAU3m5vYQMaViVPoZAJIeMnRCi_ch7bShfunOhH2wwzhiyplT8Se8U5dFv1DvVOFi0fl38HoAI2F8Kt0MhIoJAov14ZpPLsDh59Gsn14-AJTrupzcD0T1UGtNvg4B8STfqDCGroqqT-rl_O_w44ci1gYIBmaGHGBA52KNsgOlqD4zQfDu_UIIvsi0YGwp1ja4P8ix8OxajhYRqHnnkFiugJCwMRCnQw5Gw4xZPOAdclL08w_LFEc4QLEKBMC057kjA51FVA8CtG1hs7LGigaVhO3hTI90iyzM3eXx42qGFIJajK9mAuLLUsGksW6sWGE136ixZvsZRQNpEWjKvbMFGOH36b173GzKLwaoq8X1l4RxHjsdcOtm0LYv4a1XCjZhExfFV9jnO6PC8Nug25jA0VRioUnJKrh7y_7Pfh7NSGotm5mhAsDemsaJ3c8R2AlN7CIlj4_C8K2eJmDsO0nh6Uh32L2U_OsuMvCGCqqVB8U2pKKZTX4="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_BywrswZzTXovyCJataXXnhR7", "id": "fc_05e0c4a49feda864006ab34a46ff4087d284f0b93cee93fdb3", "index": 1}]
-{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_BywrswZzTXovyCJataXXnhR7", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc5a-26c1-7043-a54b-b0aa692fcf0a</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_lUpZKgYZeq9OnvMQ1tkhu6Jj", "id": "fc_08d6966ad3cb0e2d006ab36d72f54087d28b9950f0c6f69249", "index": 0}]
+{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_lUpZKgYZeq9OnvMQ1tkhu6Jj", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce3-8a37-7ed2-8f87-da3bfa8b6e11</t>
   </si>
   <si>
     <t>{'text': 'Tool observations'}</t>
@@ -416,10 +413,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cc5a-26c8-7502-af8b-20ad6dcc4b4d</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Your input was: Tool observations", "phase": "final_answer", "index": 0, "id": "msg_05e0c4a49feda864006ab34a48031c87d29082d6c79b726828"}]</t>
+    <t>01a0cce3-8a3b-7210-9e13-45ba0f8cba7b</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_08d6966ad3cb0e2d006ab36d7406ec87d2ae7db333402af419"}]</t>
   </si>
   <si>
     <t>reference_chat_agent</t>
@@ -440,7 +437,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cc5a-133f-7620-8444-cb47a6814fbd</t>
+    <t>01a0cce3-7c5c-7951-9197-1c8eb94e74cd</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -452,7 +449,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc5a-1340-7e12-b717-479275fbf018</t>
+    <t>01a0cce3-7c5d-7d42-82e3-ec536975feca</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -473,7 +470,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc5a-178a-7050-bf38-ac8e9677d71b</t>
+    <t>01a0cce3-814e-7602-b73a-bd236698d2b2</t>
   </si>
   <si>
     <t xml:space="preserve">        echo_tool</t>
@@ -485,22 +482,22 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0cc5a-178f-7fb2-a6a0-23a30ba82704</t>
-  </si>
-  <si>
-    <t>01a0cc5a-1dc3-7021-abb1-561851a31374</t>
-  </si>
-  <si>
-    <t>01a0cc5a-1dc4-7801-ab29-de1c3584e9f8</t>
-  </si>
-  <si>
-    <t>01a0cc5a-1dc5-75a3-9e07-905a3aee5d09</t>
-  </si>
-  <si>
-    <t>01a0cc5a-26bf-7382-aa90-c362d505c483</t>
-  </si>
-  <si>
-    <t>01a0cc5a-26c4-7843-8214-e6d90a5cf77e</t>
+    <t>01a0cce3-8151-7152-8f62-bae49ced4d10</t>
+  </si>
+  <si>
+    <t>01a0cce3-863c-7092-9e70-ed4dbf898a6e</t>
+  </si>
+  <si>
+    <t>01a0cce3-863d-7742-af5c-a2c2463f1722</t>
+  </si>
+  <si>
+    <t>01a0cce3-863e-7bc2-910f-0dd0771f117e</t>
+  </si>
+  <si>
+    <t>01a0cce3-8a36-7491-9150-044fd5daba7f</t>
+  </si>
+  <si>
+    <t>01a0cce3-8a39-71f0-bfab-6793cbfd78be</t>
   </si>
 </sst>
 </file>
@@ -907,7 +904,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -967,20 +964,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E45,'Turns'!E60)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E45,'Turns'!E60),"Unknown")</f>
-        <v>0.0006591366009</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0006270508323</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F45,'Turns'!F60)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F45,'Turns'!F60),"Unknown")</f>
-        <v>0.00075557</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00071879</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>76.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -992,11 +989,11 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005195225061</v>
+        <v>0.0005153351301</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059553</v>
+        <v>0.00059073</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1004,7 +1001,7 @@
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1429,7 +1426,7 @@
         <v>105</v>
       </c>
       <c r="D26" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1">
@@ -1443,15 +1440,15 @@
         <v>106</v>
       </c>
       <c r="D27" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>6.281064e-06</v>
       </c>
       <c r="F27" s="2">
         <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E17),D27*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>1.2e-05</v>
+        <v>7.2e-06</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1510,11 +1507,11 @@
       </c>
       <c r="E31" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27)=4,SUM('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27),"Unknown")</f>
-        <v>5.44184406e-05</v>
+        <v>5.02310646e-05</v>
       </c>
       <c r="F31" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27)=4,SUM('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27),"Unknown")</f>
-        <v>6.238e-05</v>
+        <v>5.758e-05</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1536,20 +1533,20 @@
         <v>122</v>
       </c>
       <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E45,'Turns'!E60)=2,SUM('Turns'!E45,'Turns'!E60),"Unknown")</f>
-        <v>0.0001396140948</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0001117157022</v>
       </c>
       <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F45,'Turns'!F60)=2,SUM('Turns'!F45,'Turns'!F60),"Unknown")</f>
-        <v>0.00016004</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00012806</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1563,7 +1560,7 @@
         <v>94</v>
       </c>
       <c r="D33" s="4">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>95</v>
@@ -1657,15 +1654,15 @@
         <v>103</v>
       </c>
       <c r="D37" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2">
         <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.798035e-06</v>
+        <v>3.925665e-06</v>
       </c>
       <c r="F37" s="2">
         <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!D17),D37*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>5.5e-06</v>
+        <v>4.5e-06</v>
       </c>
       <c r="G37" s="5">
         <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1673,7 +1670,7 @@
       </c>
       <c r="H37" s="5">
         <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
@@ -1698,7 +1695,7 @@
         <v>105</v>
       </c>
       <c r="D39" s="4">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
@@ -1709,18 +1706,18 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D40" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2">
         <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.9890036e-05</v>
       </c>
       <c r="F40" s="2">
-        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!F17),D40*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.92e-05</v>
+        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!E17),D40*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
       </c>
       <c r="G40" s="5">
         <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1731,7 +1728,7 @@
         <v>2.0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
+    <row r="41" spans="1:13" ht="73" customHeight="1">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -1739,29 +1736,13 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="5">
-        <v>21</v>
-      </c>
-      <c r="E41" s="2">
-        <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
-      </c>
-      <c r="F41" s="2">
-        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!E17),D41*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H41" s="5">
-        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="281" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -1769,10 +1750,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="24" customHeight="1">
@@ -1783,61 +1761,61 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="24" customHeight="1">
-      <c r="A44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="4">
         <v>2</v>
       </c>
-      <c r="C44" t="s">
-        <v>104</v>
+      <c r="C44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="2">
+        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40)=4,SUM('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40),"Unknown")</f>
+        <v>6.0542478e-05</v>
+      </c>
+      <c r="F44" s="2">
+        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40)=4,SUM('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40),"Unknown")</f>
+        <v>6.94e-05</v>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H44" s="5">
+        <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A45" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="B45" s="4">
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40,'Turns'!E41)=5,SUM('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40,'Turns'!E41),"Unknown")</f>
-        <v>8.025804e-05</v>
-      </c>
-      <c r="F45" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40,'Turns'!F41)=5,SUM('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40,'Turns'!F41),"Unknown")</f>
-        <v>9.2e-05</v>
-      </c>
-      <c r="G45" s="5">
-        <f>IF(ISNUMBER(E45),ROUND(E45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H45" s="5">
-        <f>IF(ISNUMBER(F45),ROUND(F45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>111</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B46" s="4">
+      <c r="M45" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="24" customHeight="1">
+      <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M46" s="4" t="s">
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1846,270 +1824,259 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="24" customHeight="1">
-      <c r="B48">
+    <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="4">
         <v>2</v>
       </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
-      <c r="I48" s="6" t="s">
+      <c r="C48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2132</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="24" customHeight="1">
+      <c r="A49" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="4">
+      <c r="B49">
         <v>2</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D49" s="4">
-        <v>2154</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24" customHeight="1">
+      <c r="C49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2093</v>
+      </c>
+      <c r="E49" s="2">
+        <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.65174082e-05</v>
+      </c>
+      <c r="F49" s="2">
+        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C17),D49*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.186e-05</v>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="24" customHeight="1">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D50" s="5">
-        <v>2097</v>
+        <v>3</v>
       </c>
       <c r="E50" s="2">
         <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.65871978e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.194e-05</v>
+        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G50" s="5">
         <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H50" s="5">
         <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="5">
-        <v>3</v>
-      </c>
-      <c r="E51" s="2">
-        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!B17),D51*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G51" s="5">
-        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="5">
-        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24" customHeight="1">
+        <v>120</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
-      </c>
-      <c r="I52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="5">
+        <v>36</v>
+      </c>
+      <c r="E52" s="2">
+        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.85133e-06</v>
+      </c>
+      <c r="F52" s="2">
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!D17),D52*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>9e-06</v>
+      </c>
+      <c r="G52" s="5">
+        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="24" customHeight="1">
+      <c r="A53" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
-      <c r="A53" t="s">
-        <v>131</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="5">
-        <v>54</v>
-      </c>
-      <c r="E53" s="2">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.1776995e-05</v>
-      </c>
-      <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.35e-05</v>
-      </c>
-      <c r="G53" s="5">
-        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="4">
+        <v>2</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="24" customHeight="1">
+      <c r="A55" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="5">
+        <v>6</v>
+      </c>
+      <c r="E55" s="2">
+        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.281064e-06</v>
+      </c>
+      <c r="F55" s="2">
+        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G55" s="5">
+        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
         <v>1.0</v>
       </c>
-      <c r="H53" s="5">
-        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H55" s="5">
+        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
         <v>1.0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="24" customHeight="1">
-      <c r="A54" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="4">
-        <v>2</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
+    <row r="56" spans="1:11" ht="34" customHeight="1">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" s="5">
-        <v>10</v>
-      </c>
-      <c r="E56" s="2">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.046844e-05</v>
-      </c>
-      <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!E17),D56*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>1.2e-05</v>
-      </c>
-      <c r="G56" s="5">
-        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H56" s="5">
-        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="34" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="24" customHeight="1">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
-      <c r="A59" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="4">
         <v>2</v>
       </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B60" s="4">
-        <v>2</v>
-      </c>
-      <c r="C60" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E60" s="2">
-        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56)=4,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56),"Unknown")</f>
-        <v>5.93560548e-05</v>
-      </c>
-      <c r="F60" s="2">
-        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56)=4,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56),"Unknown")</f>
-        <v>6.804e-05</v>
-      </c>
-      <c r="G60" s="5">
-        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E59" s="2">
+        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55)=4,SUM('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55),"Unknown")</f>
+        <v>5.11732242e-05</v>
+      </c>
+      <c r="F59" s="2">
+        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55)=4,SUM('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55),"Unknown")</f>
+        <v>5.866e-05</v>
+      </c>
+      <c r="G59" s="5">
+        <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H59" s="5">
+        <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
         <v>6.0</v>
       </c>
-      <c r="H60" s="5">
-        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="K60" s="4" t="s">
+      <c r="K59" s="4" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE60">
+  <conditionalFormatting sqref="A2:AE59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2230,13 +2197,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -2245,7 +2212,7 @@
         <v>110</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -2288,15 +2255,15 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D27)=2,SUM('Turns'!D12,'Turns'!D27),"Unknown")</f>
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E27)=2,SUM('Turns'!E12,'Turns'!E27),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>2.61711e-05</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F27)=2,SUM('Turns'!F12,'Turns'!F27),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -2309,11 +2276,11 @@
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005195225061</v>
+        <v>0.0005153351301</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059553</v>
+        <v>0.00059073</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2321,24 +2288,24 @@
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2674.768</v>
+        <v>2500.339</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -2347,30 +2314,30 @@
         <v>110</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" t="s">
         <v>139</v>
-      </c>
-      <c r="H3" t="s">
-        <v>140</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.409</v>
+        <v>0.381</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -2379,10 +2346,10 @@
         <v>110</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" t="s">
         <v>143</v>
-      </c>
-      <c r="H4" t="s">
-        <v>144</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -2458,21 +2425,21 @@
         <v>53.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1096.278</v>
+        <v>1264.32</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
@@ -2484,13 +2451,13 @@
         <v>2042</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -2566,21 +2533,21 @@
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1088.935</v>
+        <v>1257.694</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -2589,30 +2556,30 @@
         <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" t="s">
         <v>150</v>
-      </c>
-      <c r="H6" t="s">
-        <v>151</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>4.222</v>
+        <v>1.954</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -2621,30 +2588,30 @@
         <v>110</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
         <v>112</v>
       </c>
       <c r="I7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.654</v>
+        <v>0.504</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -2653,10 +2620,10 @@
         <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -2699,15 +2666,15 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>6.281064e-06</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>7.2e-06</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2720,11 +2687,11 @@
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.44184406e-05</v>
+        <v>5.02310646e-05</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>6.238e-05</v>
+        <v>5.758e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2735,21 +2702,21 @@
         <v>6.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1568.847</v>
+        <v>1229.084</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>95</v>
@@ -2761,13 +2728,13 @@
         <v>2078</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H9" t="s">
         <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J9" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -2807,15 +2774,15 @@
       </c>
       <c r="S9" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>6.281064e-06</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>7.2e-06</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2828,11 +2795,11 @@
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.44184406e-05</v>
+        <v>5.02310646e-05</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>6.238e-05</v>
+        <v>5.758e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2846,21 +2813,21 @@
         <v>117</v>
       </c>
       <c r="AD9" s="1">
-        <v>1563.935</v>
+        <v>1225.263</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -2869,103 +2836,100 @@
         <v>110</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35,'Turns'!D50)=2,SUM('Turns'!D35,'Turns'!D50),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E51)=2,SUM('Turns'!E35,'Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
         <v>1.046844e-06</v>
       </c>
       <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F51)=2,SUM('Turns'!F35,'Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M10" s="2">
-        <f>IF(COUNT('Turns'!D34,'Turns'!D50)=2,SUM('Turns'!D34,'Turns'!D50),"Unknown")</f>
-        <v>4172.0</v>
+        <f>IF(COUNT('Turns'!D34,'Turns'!D49)=2,SUM('Turns'!D34,'Turns'!D49),"Unknown")</f>
+        <v>4168.0</v>
       </c>
       <c r="N10" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
-        <v>7.27905528e-05</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>7.27207632e-05</v>
       </c>
       <c r="O10" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
-        <v>8.344e-05</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>8.336e-05</v>
       </c>
       <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D37,'Turns'!D53)=2,SUM('Turns'!D37,'Turns'!D53),"Unknown")</f>
-        <v>76.0</v>
+        <f>IF(COUNT('Turns'!D37,'Turns'!D52)=2,SUM('Turns'!D37,'Turns'!D52),"Unknown")</f>
+        <v>54.0</v>
       </c>
       <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E37,'Turns'!E53)=2,SUM('Turns'!E37,'Turns'!E53),"Unknown")</f>
-        <v>1.657503e-05</v>
+        <f>IF(COUNT('Turns'!E37,'Turns'!E52)=2,SUM('Turns'!E37,'Turns'!E52),"Unknown")</f>
+        <v>1.1776995e-05</v>
       </c>
       <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F37,'Turns'!F53)=2,SUM('Turns'!F37,'Turns'!F53),"Unknown")</f>
-        <v>1.9e-05</v>
+        <f>IF(COUNT('Turns'!F37,'Turns'!F52)=2,SUM('Turns'!F37,'Turns'!F52),"Unknown")</f>
+        <v>1.35e-05</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D41,'Turns'!D56)=2,SUM('Turns'!D41,'Turns'!D56),"Unknown")</f>
-        <v>31.0</v>
+        <f>IF(COUNT('Turns'!D40,'Turns'!D55)=2,SUM('Turns'!D40,'Turns'!D55),"Unknown")</f>
+        <v>25.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E41,'Turns'!E56)=2,SUM('Turns'!E41,'Turns'!E56),"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <f>IF(COUNT('Turns'!E40,'Turns'!E55)=2,SUM('Turns'!E40,'Turns'!E55),"Unknown")</f>
+        <v>2.61711e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F41,'Turns'!F56)=2,SUM('Turns'!F41,'Turns'!F56),"Unknown")</f>
-        <v>3.72e-05</v>
+        <f>IF(COUNT('Turns'!F40,'Turns'!F55)=2,SUM('Turns'!F40,'Turns'!F55),"Unknown")</f>
+        <v>3e-05</v>
       </c>
       <c r="V10" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>16.0</v>
+        <v>0</v>
       </c>
       <c r="W10" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>0</v>
       </c>
       <c r="X10" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>1.92e-05</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E45,'Turns'!E60)=2,SUM('Turns'!E45,'Turns'!E60),"Unknown")</f>
-        <v>0.0001396140948</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0001117157022</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F45,'Turns'!F60)=2,SUM('Turns'!F45,'Turns'!F60),"Unknown")</f>
-        <v>0.00016004</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00012806</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>3152.6</v>
+        <v>2136.051</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -2974,30 +2938,30 @@
         <v>110</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.278</v>
+        <v>0.399</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -3006,13 +2970,13 @@
         <v>110</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J12" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -3040,72 +3004,69 @@
       </c>
       <c r="P12" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="Q12" s="2">
         <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>4.798035e-06</v>
+        <v>3.925665e-06</v>
       </c>
       <c r="R12" s="2">
         <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>5.5e-06</v>
+        <v>4.5e-06</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>1.9890036e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V12" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>16.0</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>1.92e-05</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.025804e-05</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>6.0542478e-05</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.2e-05</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>6.94e-05</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2295.766</v>
+        <v>1015.11</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
@@ -3114,16 +3075,16 @@
         <v>110</v>
       </c>
       <c r="F13" s="1">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H13" t="s">
         <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -3151,75 +3112,72 @@
       </c>
       <c r="P13" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="Q13" s="2">
         <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>4.798035e-06</v>
+        <v>3.925665e-06</v>
       </c>
       <c r="R13" s="2">
         <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>5.5e-06</v>
+        <v>4.5e-06</v>
       </c>
       <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>1.9890036e-05</v>
       </c>
       <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V13" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>16.0</v>
+        <v>0</v>
       </c>
       <c r="W13" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>0</v>
       </c>
       <c r="X13" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>1.92e-05</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.025804e-05</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>6.0542478e-05</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.2e-05</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>6.94e-05</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AD13" s="1">
-        <v>2290.214</v>
+        <v>1010.229</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -3228,30 +3186,30 @@
         <v>110</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AD14" s="1">
-        <v>3.686</v>
+        <v>1.659</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -3260,30 +3218,30 @@
         <v>110</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD15" s="1">
-        <v>1.13</v>
+        <v>0.466</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -3292,61 +3250,61 @@
         <v>110</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2097.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>2093.0</v>
       </c>
       <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>3.65871978e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>3.65174082e-05</v>
       </c>
       <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.194e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>4.186e-05</v>
       </c>
       <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>54.0</v>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>1.1776995e-05</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>7.85133e-06</v>
       </c>
       <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>1.35e-05</v>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>10.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>6.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>6.281064e-06</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>1.2e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>7.2e-06</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
@@ -3358,37 +3316,37 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>5.93560548e-05</v>
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>5.11732242e-05</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>6.804e-05</v>
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>5.866e-05</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>845.699</v>
+        <v>1114.33</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>95</v>
@@ -3397,64 +3355,64 @@
         <v>110</v>
       </c>
       <c r="F17" s="1">
-        <v>2154</v>
+        <v>2132</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2097.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>2093.0</v>
       </c>
       <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>3.65871978e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>3.65174082e-05</v>
       </c>
       <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.194e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>4.186e-05</v>
       </c>
       <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>54.0</v>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>1.1776995e-05</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>7.85133e-06</v>
       </c>
       <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>1.35e-05</v>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>10.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>6.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>6.281064e-06</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>1.2e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>7.2e-06</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -3466,29 +3424,29 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>5.93560548e-05</v>
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>5.11732242e-05</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>6.804e-05</v>
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>5.866e-05</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD17" s="1">
-        <v>839.609</v>
+        <v>1110.728</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tool_chat/report.xlsx
+++ b/reports/tool_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="161">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce3-7c59-7500-9bb3-9e974c30762a</t>
+    <t>01a0d143-3bb2-7940-aa9a-fce8e789c19e</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,13 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce3-7c62-7600-b525-c91ab3e30b57</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d143-3bbf-7260-86c0-80fcd5038b6f</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -342,8 +345,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_aqkxBJdFbfYxEHqTsjw3OgFh", "id": "fc_08d6966ad3cb0e2d006ab36d70b7f487d28768709fe626665a", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_aqkxBJdFbfYxEHqTsjw3OgFh", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_kA1D7fN7irmL7RwLmk8I9Bpq", "id": "fc_0eb7081bb50e1523006ab48c18869887d2be54906e314498bf", "index": 0}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_kA1D7fN7irmL7RwLmk8I9Bpq", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,7 +358,7 @@
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0cce3-814f-7662-9b6a-9b765682d148</t>
+    <t>01a0d143-40d9-76c3-a8ac-560f6e865c97</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -373,16 +376,13 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce3-8153-7ff3-bd84-ba4dd62a9af7</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0d143-40de-7e43-b592-8c445294b22c</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_08d6966ad3cb0e2d006ab36d71e44487d293994b9490428e9d"}]</t>
+    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_0eb7081bb50e1523006ab48c19675087d29493951e24343daa"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -391,17 +391,20 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cce3-8641-7331-a98e-1aa32356ee5c</t>
+    <t>01a0d143-4427-79f2-9714-0f513991f047</t>
   </si>
   <si>
     <t>Echo this text: Tool observations</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_lUpZKgYZeq9OnvMQ1tkhu6Jj", "id": "fc_08d6966ad3cb0e2d006ab36d72f54087d28b9950f0c6f69249", "index": 0}]
-{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_lUpZKgYZeq9OnvMQ1tkhu6Jj", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce3-8a37-7ed2-8f87-da3bfa8b6e11</t>
+    <t>Reasoning</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0eb7081bb50e1523006ab48c1a3fcc87d2b53434a0d7c1b0d3", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwaGso6agc0GulrjhK0U9jq7JXxfGLA4j27UZKGBFmDLXceyKl5se4I4-pJK7CMDhupaHPDh8d-h4zr1PHqiWNZ-dBSx4VJQbYHvf2RyFvcPRP4KRx-k5GrkWvw5IZdWwtgbC10-wf8PPvIW55YKDQ0SOYsApzb7jhaBTHJ0bWXpDniFLuM8KrH_NNioWX0nb-qy-g8pmDEqi-6DUzZcrCRVAKKKv_TBnapaLOJQsCf0cZaRR6ufRCyFxm2fIWEyvLZYQtH5JU2B7-rVnLukGGkADbFBFELkOeQn8kByz8nYAdq0FyXj2Ys6E6ay75TVhesOS71gyFuXY2Dge2k3XMHTDHopBxaW7ahlfzKp8pWjXE-PPXyNtv8l43SWrqfIWV8sqQEwJu8vJs8-YK-8EaqWGTKoWe4AZ_UNewiAxIlO1mGBOx4dpa5Cg9MrPT2BkT9aQwhBkd6dg_v5XlBjaTsvGiADyiFMOSwnsdRYjbLBobFRSVnv1vSttpiFxGszIi-cIKIO5C7x4Bld2saFs5aiFnZkU_i2JYvRnh21OF9eIyGSG28rEOnZ3RxuNwJP-4PLisxAmOS9byaYAVt5owdN4fpJYd-BEhhCT2DWJGHW9P_tjZo78SFl7nxi-sFUqHSK24REwxbiAgD48t9Zcvi68SomEmqzhwAkSORHmeckNx9Klwb3wqlsUh59mzl8Cq_96ekQW6EeJox7cRTjJxwhSTuShj37zfjeICmwzMZ2Wgyj8VkcRqUp4hHRfOt5yB3G17DLXaeXTixyMeWuxp7StsJ1sHl_srA0MTVS52ZE-g_1aZogaiDl1oG9nNF8L_LPEa2l19O4aiUHD3Mz-eSTmfW7cR4ICu9GhoAopz8t63IyeOl095Nfdx36jTmojl59dGrpBCFa5zq3yPYr7p-5kXwTs7P7RITtSF4GqLbNXWCG7g7XkSrhp7Kl8BZF7-Y2qwsYoU6mU8b4lKUjlkfDrj8BvFX_W3fgoBDOXlb6NK9SUSYLx0lD2E6PkmmVKz3pFMqC4XDy2aQRBNIML-InftahiXRjOElavBF0iHeCc-qZmXKhmB2pd6V9d7dNz2RIQkKlMFAxyUBy_d6EWCEc9OFaL2bJw1bFIWZZ6ZDcMNQ4w7WUXvk9KT4cS8Zw71uvBJwnFu8gURoIQ7d7os0P3eyoPL-A9UFkWB2gUPy9yZy44cpAykXXFUImRr7JjpsxRwimzgPhx-ubM_1auctvQ=="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_LeB7y3SoyKUgNjggdMJ6Dx5A", "id": "fc_0eb7081bb50e1523006ab48c1a76f487d2a56298a4b976763f", "index": 1}]
+{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_LeB7y3SoyKUgNjggdMJ6Dx5A", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d143-4822-7592-abb8-a192231f660c</t>
   </si>
   <si>
     <t>{'text': 'Tool observations'}</t>
@@ -413,10 +416,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cce3-8a3b-7210-9e13-45ba0f8cba7b</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_08d6966ad3cb0e2d006ab36d7406ec87d2ae7db333402af419"}]</t>
+    <t>01a0d143-4826-7d41-a4ee-678b4e800ed4</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_0eb7081bb50e1523006ab48c1b45f487d2bf90a9804b1e282e"}]</t>
   </si>
   <si>
     <t>reference_chat_agent</t>
@@ -437,7 +440,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cce3-7c5c-7951-9197-1c8eb94e74cd</t>
+    <t>01a0d143-3bb5-7aa1-9449-38d127073f39</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -449,7 +452,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce3-7c5d-7d42-82e3-ec536975feca</t>
+    <t>01a0d143-3bb7-7be1-ad34-30d011c64278</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -470,7 +473,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce3-814e-7602-b73a-bd236698d2b2</t>
+    <t>01a0d143-40d8-7902-9c77-d790dfc2bd1e</t>
   </si>
   <si>
     <t xml:space="preserve">        echo_tool</t>
@@ -482,22 +485,22 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0cce3-8151-7152-8f62-bae49ced4d10</t>
-  </si>
-  <si>
-    <t>01a0cce3-863c-7092-9e70-ed4dbf898a6e</t>
-  </si>
-  <si>
-    <t>01a0cce3-863d-7742-af5c-a2c2463f1722</t>
-  </si>
-  <si>
-    <t>01a0cce3-863e-7bc2-910f-0dd0771f117e</t>
-  </si>
-  <si>
-    <t>01a0cce3-8a36-7491-9150-044fd5daba7f</t>
-  </si>
-  <si>
-    <t>01a0cce3-8a39-71f0-bfab-6793cbfd78be</t>
+    <t>01a0d143-40db-7542-88cb-cff6fca5b6af</t>
+  </si>
+  <si>
+    <t>01a0d143-4422-77d3-8086-047757b74f60</t>
+  </si>
+  <si>
+    <t>01a0d143-4423-7c01-b795-eba8af788806</t>
+  </si>
+  <si>
+    <t>01a0d143-4424-7793-aa4b-11ab024442cf</t>
+  </si>
+  <si>
+    <t>01a0d143-4821-7d11-a275-fa61bc1573df</t>
+  </si>
+  <si>
+    <t>01a0d143-4824-71a2-8856-10fda9df80b6</t>
   </si>
 </sst>
 </file>
@@ -904,7 +907,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -964,20 +967,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0006270508323</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61)=4,SUM('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61),"Unknown")</f>
+        <v>0.0002271061025</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00071879</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61)=4,SUM('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61),"Unknown")</f>
+        <v>0.00025915</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>63.0</v>
+        <v>23.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>72.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -988,20 +991,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005153351301</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>9.9448198e-05</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059073</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00011348</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>10.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1035,23 +1038,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>2039</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.5737553e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.078e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1064,8 +1067,27 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="34" customHeight="1">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1075,11 +1097,8 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="34" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1087,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1101,26 +1120,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2039</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0004446906075</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00050975</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1134,51 +1137,32 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="4">
+    </row>
+    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="5">
-        <v>19</v>
-      </c>
-      <c r="E12" s="2">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.9890036e-05</v>
-      </c>
-      <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="73" customHeight="1">
+    <row r="13" spans="1:13" ht="24" customHeight="1">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -1188,11 +1172,27 @@
       <c r="C13" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1">
+      <c r="D13" s="5">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.998078e-05</v>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
+      </c>
+      <c r="G13" s="5">
+        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="5">
+        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="73" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1200,7 +1200,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
@@ -1214,59 +1217,59 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:13" ht="24" customHeight="1">
+      <c r="A16" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12)=3,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12),"Unknown")</f>
-        <v>0.0004651040655</v>
-      </c>
-      <c r="F16" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12)=3,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12),"Unknown")</f>
-        <v>0.00053315</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="H16" s="5">
-        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>110</v>
+      <c r="C16" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13),"Unknown")</f>
+        <v>5.6244143e-05</v>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13),"Unknown")</f>
+        <v>6.418e-05</v>
+      </c>
+      <c r="G17" s="5">
+        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M17" s="4" t="s">
+    </row>
+    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="24" customHeight="1">
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="K18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1">
@@ -1274,65 +1277,46 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:13" ht="24" customHeight="1">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="I20" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="4">
+    </row>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D21" s="4">
         <v>2078</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="24" customHeight="1">
-      <c r="A21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="M21" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D21" s="5">
-        <v>2039</v>
-      </c>
-      <c r="E21" s="2">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.55752486e-05</v>
-      </c>
-      <c r="F21" s="2">
-        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C17),D21*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.078e-05</v>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H21" s="5">
-        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1341,72 +1325,72 @@
         <v>97</v>
       </c>
       <c r="D22" s="5">
-        <v>3</v>
+        <v>2075</v>
       </c>
       <c r="E22" s="2">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.6368525e-05</v>
       </c>
       <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B17),D22*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!C17),D22*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.15e-05</v>
       </c>
       <c r="G22" s="5">
         <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H22" s="5">
         <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>116</v>
+        <v>98</v>
+      </c>
+      <c r="D23" s="5">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F23" s="2">
+        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G23" s="5">
+        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="5">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2">
-        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.85133e-06</v>
-      </c>
-      <c r="F24" s="2">
-        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!D17),D24*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>9e-06</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="5">
-        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>120</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1415,53 +1399,34 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="4">
+    <row r="26" spans="1:13" ht="24" customHeight="1">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="4">
+    </row>
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="24" customHeight="1">
-      <c r="A27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="5">
-        <v>6</v>
-      </c>
-      <c r="E27" s="2">
-        <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.281064e-06</v>
-      </c>
-      <c r="F27" s="2">
-        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E17),D27*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="G27" s="5">
-        <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H27" s="5">
-        <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="34" customHeight="1">
+    <row r="28" spans="1:13" ht="24" customHeight="1">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1469,24 +1434,43 @@
       <c r="C28" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
+      <c r="D28" s="5">
+        <v>6</v>
+      </c>
+      <c r="E28" s="2">
+        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.30972e-06</v>
+      </c>
+      <c r="F28" s="2">
+        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G28" s="5">
+        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="34" customHeight="1">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1495,108 +1479,89 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="4">
+    <row r="31" spans="1:13" ht="24" customHeight="1">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27)=4,SUM('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27),"Unknown")</f>
-        <v>5.02310646e-05</v>
-      </c>
-      <c r="F31" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27)=4,SUM('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27),"Unknown")</f>
-        <v>5.758e-05</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H31" s="5">
-        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K31" s="4" t="s">
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B32" s="4">
-        <v>2</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0001117157022</v>
+        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E28)=3,SUM('Turns'!E22,'Turns'!E23,'Turns'!E28),"Unknown")</f>
+        <v>4.3204055e-05</v>
       </c>
       <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00012806</v>
+        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F28)=3,SUM('Turns'!F22,'Turns'!F23,'Turns'!F28),"Unknown")</f>
+        <v>4.93e-05</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="B33" s="4">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="2">
+        <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
+        <v>0.0001276579045</v>
+      </c>
+      <c r="F33" s="2">
+        <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
+        <v>0.00014567</v>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="H33" s="5">
+        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D34" s="4">
         <v>2096</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J34" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M33" s="4" t="s">
+      <c r="M34" s="4" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1">
-      <c r="A34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2075</v>
-      </c>
-      <c r="E34" s="2">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6203355e-05</v>
-      </c>
-      <c r="F34" s="2">
-        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!C17),D34*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.15e-05</v>
-      </c>
-      <c r="G34" s="5">
-        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H34" s="5">
-        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1">
@@ -1610,23 +1575,23 @@
         <v>97</v>
       </c>
       <c r="D35" s="5">
-        <v>3</v>
+        <v>2093</v>
       </c>
       <c r="E35" s="2">
         <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.6684011e-05</v>
       </c>
       <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!B17),D35*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!C17),D35*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.186e-05</v>
       </c>
       <c r="G35" s="5">
         <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H35" s="5">
         <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1">
@@ -1637,10 +1602,26 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>125</v>
+        <v>98</v>
+      </c>
+      <c r="D36" s="5">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!B17),D36*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
@@ -1651,26 +1632,10 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="5">
-        <v>18</v>
-      </c>
-      <c r="E37" s="2">
-        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.925665e-06</v>
-      </c>
-      <c r="F37" s="2">
-        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!D17),D37*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.5e-06</v>
-      </c>
-      <c r="G37" s="5">
-        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="5">
-        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>102</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
@@ -1684,51 +1649,32 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:13" ht="24" customHeight="1">
+      <c r="A39" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39">
         <v>2</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="24" customHeight="1">
-      <c r="A40" t="s">
+    </row>
+    <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="4">
         <v>2</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="5">
-        <v>19</v>
-      </c>
-      <c r="E40" s="2">
-        <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.9890036e-05</v>
-      </c>
-      <c r="F40" s="2">
-        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!E17),D40*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="G40" s="5">
-        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H40" s="5">
-        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="73" customHeight="1">
+      <c r="D40" s="4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="24" customHeight="1">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -1736,10 +1682,26 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="6" t="s">
         <v>126</v>
+      </c>
+      <c r="D41" s="5">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2">
+        <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.367106e-05</v>
+      </c>
+      <c r="F41" s="2">
+        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!F17),D41*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>1.56e-05</v>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H41" s="5">
+        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
@@ -1750,10 +1712,29 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D42" s="5">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2">
+        <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.208402e-05</v>
+      </c>
+      <c r="F42" s="2">
+        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E17),D42*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.52e-05</v>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="281" customHeight="1">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -1761,322 +1742,347 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>108</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A44" s="4" t="s">
+    <row r="45" spans="1:13" ht="24" customHeight="1">
+      <c r="A45" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B45">
         <v>2</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40)=4,SUM('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40),"Unknown")</f>
-        <v>6.0542478e-05</v>
-      </c>
-      <c r="F44" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40)=4,SUM('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40),"Unknown")</f>
-        <v>6.94e-05</v>
-      </c>
-      <c r="G44" s="5">
-        <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H44" s="5">
-        <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="4">
+        <v>2</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="2">
+        <f>IF(COUNT('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42)=4,SUM('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42),"Unknown")</f>
+        <v>7.2964901e-05</v>
+      </c>
+      <c r="F46" s="2">
+        <f>IF(COUNT('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42)=4,SUM('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42),"Unknown")</f>
+        <v>8.326e-05</v>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
         <v>7.0</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B45" s="4">
+      <c r="H46" s="5">
+        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B47" s="4">
         <v>2</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C47" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K45" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="24" customHeight="1">
-      <c r="B46">
+      <c r="M47" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="24" customHeight="1">
+      <c r="B48">
         <v>2</v>
       </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="24" customHeight="1">
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="I47" s="6" t="s">
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A48" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" s="4">
-        <v>2</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48" s="4">
-        <v>2132</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="24" customHeight="1">
-      <c r="A49" t="s">
-        <v>130</v>
-      </c>
+    <row r="49" spans="1:13" ht="24" customHeight="1">
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2093</v>
-      </c>
-      <c r="E49" s="2">
-        <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.65174082e-05</v>
-      </c>
-      <c r="F49" s="2">
-        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C17),D49*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="G49" s="5">
-        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H49" s="5">
-        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="24" customHeight="1">
-      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B50">
+    </row>
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4">
         <v>2</v>
       </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="5">
-        <v>3</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="24" customHeight="1">
+      <c r="C50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="4">
+        <v>2147</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="24" customHeight="1">
+        <v>97</v>
+      </c>
+      <c r="D51" s="5">
+        <v>2093</v>
+      </c>
+      <c r="E51" s="2">
+        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.6684011e-05</v>
+      </c>
+      <c r="F51" s="2">
+        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.186e-05</v>
+      </c>
+      <c r="G51" s="5">
+        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H51" s="5">
+        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D52" s="5">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2">
         <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.85133e-06</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!D17),D52*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>9e-06</v>
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="24" customHeight="1">
       <c r="A53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
+        <v>120</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="24" customHeight="1">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="4">
-        <v>2</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="24" customHeight="1">
+      <c r="D54" s="5">
+        <v>51</v>
+      </c>
+      <c r="E54" s="2">
+        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.11734625e-05</v>
+      </c>
+      <c r="F54" s="2">
+        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>1.275e-05</v>
+      </c>
+      <c r="G54" s="5">
+        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="24" customHeight="1">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="4">
+        <v>2</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D56" s="4">
         <v>6</v>
       </c>
-      <c r="E55" s="2">
-        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.281064e-06</v>
-      </c>
-      <c r="F55" s="2">
-        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="G55" s="5">
-        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H55" s="5">
-        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="34" customHeight="1">
-      <c r="A56" t="s">
-        <v>130</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="24" customHeight="1">
+    </row>
+    <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D57" s="5">
+        <v>6</v>
+      </c>
+      <c r="E57" s="2">
+        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.30972e-06</v>
+      </c>
+      <c r="F57" s="2">
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G57" s="5">
+        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H57" s="5">
+        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="34" customHeight="1">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
+        <v>108</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="24" customHeight="1">
+      <c r="A59" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="60" spans="1:13" ht="24" customHeight="1">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60">
         <v>2</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E59" s="2">
-        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55)=4,SUM('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55),"Unknown")</f>
-        <v>5.11732242e-05</v>
-      </c>
-      <c r="F59" s="2">
-        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55)=4,SUM('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55),"Unknown")</f>
-        <v>5.866e-05</v>
-      </c>
-      <c r="G59" s="5">
-        <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="C60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A61" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="4">
+        <v>2</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E61" s="2">
+        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57)=4,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57),"Unknown")</f>
+        <v>5.46930035e-05</v>
+      </c>
+      <c r="F61" s="2">
+        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57)=4,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57),"Unknown")</f>
+        <v>6.241e-05</v>
+      </c>
+      <c r="G61" s="5">
+        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
         <v>5.0</v>
       </c>
-      <c r="H59" s="5">
-        <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H61" s="5">
+        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
         <v>6.0</v>
       </c>
-      <c r="K59" s="4" t="s">
-        <v>110</v>
+      <c r="K61" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE59">
+  <conditionalFormatting sqref="A2:AE61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2197,72 +2203,69 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
+        <f>IF(COUNT('Turns'!D6,'Turns'!D23)=2,SUM('Turns'!D6,'Turns'!D23),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K2" s="2">
+        <f>IF(COUNT('Turns'!E6,'Turns'!E23)=2,SUM('Turns'!E6,'Turns'!E23),"Unknown")</f>
+        <v>1.05162e-06</v>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(COUNT('Turns'!F6,'Turns'!F23)=2,SUM('Turns'!F6,'Turns'!F23),"Unknown")</f>
+        <v>1.2e-06</v>
+      </c>
+      <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D22)=2,SUM('Turns'!D5,'Turns'!D22),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K2" s="2">
+        <v>4114.0</v>
+      </c>
+      <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E22)=2,SUM('Turns'!E5,'Turns'!E22),"Unknown")</f>
-        <v>1.046844e-06</v>
-      </c>
-      <c r="L2" s="2">
+        <v>7.2106078e-05</v>
+      </c>
+      <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F22)=2,SUM('Turns'!F5,'Turns'!F22),"Unknown")</f>
-        <v>1.2e-06</v>
-      </c>
-      <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
-      </c>
-      <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.55752486e-05</v>
-      </c>
-      <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <v>8.228e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D24)=2,SUM('Turns'!D9,'Turns'!D24),"Unknown")</f>
-        <v>2075.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E24)=2,SUM('Turns'!E9,'Turns'!E24),"Unknown")</f>
-        <v>0.0004525419375</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F24)=2,SUM('Turns'!F9,'Turns'!F24),"Unknown")</f>
-        <v>0.00051875</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D27)=2,SUM('Turns'!D12,'Turns'!D27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
         <v>25.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E27)=2,SUM('Turns'!E12,'Turns'!E27),"Unknown")</f>
-        <v>2.61711e-05</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
+        <v>2.62905e-05</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F27)=2,SUM('Turns'!F12,'Turns'!F27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
         <v>3e-05</v>
       </c>
       <c r="V2" s="2">
@@ -2275,128 +2278,128 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005153351301</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>9.9448198e-05</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059073</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00011348</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>10.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>11.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2500.339</v>
+        <v>2137.39</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.381</v>
+        <v>0.497</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
       </c>
       <c r="J4" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K4" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L4" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K4" s="2">
+        <v>2039.0</v>
+      </c>
+      <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L4" s="2">
+        <v>3.5737553e-05</v>
+      </c>
+      <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
+        <v>4.078e-05</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2039.0</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0004446906075</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00050975</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>19.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.9890036e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>1.998078e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>2.28e-05</v>
       </c>
       <c r="V4" s="2">
@@ -2409,99 +2412,99 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.0004651040655</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>5.6244143e-05</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.00053315</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>6.418e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>6.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1264.32</v>
+        <v>1312.13</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1">
         <v>2042</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J5" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L5" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2039.0</v>
+      </c>
+      <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L5" s="2">
+        <v>3.5737553e-05</v>
+      </c>
+      <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
+        <v>4.078e-05</v>
       </c>
       <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2039.0</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0004446906075</v>
+        <v>0</v>
       </c>
       <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00050975</v>
+        <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>19.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.9890036e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>1.998078e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>2.28e-05</v>
       </c>
       <c r="V5" s="2">
@@ -2514,166 +2517,163 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.0004651040655</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>5.6244143e-05</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.00053315</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>6.418e-05</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>6.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1257.694</v>
+        <v>1301.829</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>1.954</v>
+        <v>2.268</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.504</v>
+        <v>0.59</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="2">
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L8" s="2">
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M8" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="2">
+        <v>2075.0</v>
+      </c>
+      <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L8" s="2">
+        <v>3.6368525e-05</v>
+      </c>
+      <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
-      </c>
-      <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.55752486e-05</v>
-      </c>
-      <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <v>4.15e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>7.85133e-06</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>6.281064e-06</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>6.30972e-06</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V8" s="2">
@@ -2686,102 +2686,99 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.02310646e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>4.3204055e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.758e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>4.93e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1229.084</v>
+        <v>817.1180000000001</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1">
         <v>2078</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J9" s="2">
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L9" s="2">
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M9" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K9" s="2">
+        <v>2075.0</v>
+      </c>
+      <c r="N9" s="2">
         <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L9" s="2">
+        <v>3.6368525e-05</v>
+      </c>
+      <c r="O9" s="2">
         <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
-      </c>
-      <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.55752486e-05</v>
-      </c>
-      <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <v>4.15e-05</v>
       </c>
       <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>7.85133e-06</v>
+        <v>0</v>
       </c>
       <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>6.281064e-06</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>6.30972e-06</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V9" s="2">
@@ -2794,516 +2791,519 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.02310646e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>4.3204055e-05</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.758e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>4.93e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AD9" s="1">
-        <v>1225.263</v>
+        <v>812.37</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D35,'Turns'!D50)=2,SUM('Turns'!D35,'Turns'!D50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36,'Turns'!D52)=2,SUM('Turns'!D36,'Turns'!D52),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E36,'Turns'!E52)=2,SUM('Turns'!E36,'Turns'!E52),"Unknown")</f>
+        <v>1.05162e-06</v>
       </c>
       <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36,'Turns'!F52)=2,SUM('Turns'!F36,'Turns'!F52),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M10" s="2">
-        <f>IF(COUNT('Turns'!D34,'Turns'!D49)=2,SUM('Turns'!D34,'Turns'!D49),"Unknown")</f>
-        <v>4168.0</v>
+        <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
+        <v>4186.0</v>
       </c>
       <c r="N10" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
-        <v>7.27207632e-05</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E51)=2,SUM('Turns'!E35,'Turns'!E51),"Unknown")</f>
+        <v>7.3368022e-05</v>
       </c>
       <c r="O10" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
-        <v>8.336e-05</v>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F51)=2,SUM('Turns'!F35,'Turns'!F51),"Unknown")</f>
+        <v>8.372e-05</v>
       </c>
       <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D37,'Turns'!D52)=2,SUM('Turns'!D37,'Turns'!D52),"Unknown")</f>
-        <v>54.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>51.0</v>
       </c>
       <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E37,'Turns'!E52)=2,SUM('Turns'!E37,'Turns'!E52),"Unknown")</f>
-        <v>1.1776995e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>1.11734625e-05</v>
       </c>
       <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F37,'Turns'!F52)=2,SUM('Turns'!F37,'Turns'!F52),"Unknown")</f>
-        <v>1.35e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>1.275e-05</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D40,'Turns'!D55)=2,SUM('Turns'!D40,'Turns'!D55),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D42,'Turns'!D57)=2,SUM('Turns'!D42,'Turns'!D57),"Unknown")</f>
+        <v>27.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E40,'Turns'!E55)=2,SUM('Turns'!E40,'Turns'!E55),"Unknown")</f>
-        <v>2.61711e-05</v>
+        <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
+        <v>2.839374e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F40,'Turns'!F55)=2,SUM('Turns'!F40,'Turns'!F55),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
+        <v>3.24e-05</v>
       </c>
       <c r="V10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <v>13.0</v>
       </c>
       <c r="W10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>1.367106e-05</v>
       </c>
       <c r="X10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>1.56e-05</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0001117157022</v>
+        <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
+        <v>0.0001276579045</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00012806</v>
+        <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
+        <v>0.00014567</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>2136.051</v>
+        <v>1824.015</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I11" t="s">
         <v>156</v>
       </c>
-      <c r="I11" t="s">
-        <v>155</v>
-      </c>
       <c r="AD11" s="1">
-        <v>0.399</v>
+        <v>0.348</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J12" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K12" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L12" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M12" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K12" s="2">
+        <v>2093.0</v>
+      </c>
+      <c r="N12" s="2">
         <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L12" s="2">
+        <v>3.6684011e-05</v>
+      </c>
+      <c r="O12" s="2">
         <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>2075.0</v>
-      </c>
-      <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.6203355e-05</v>
-      </c>
-      <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.15e-05</v>
+        <v>4.186e-05</v>
       </c>
       <c r="P12" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>18.0</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>3.925665e-06</v>
+        <v>0</v>
       </c>
       <c r="R12" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>4.5e-06</v>
+        <v>0</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>19.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>21.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>1.9890036e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>2.208402e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>2.28e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>2.52e-05</v>
       </c>
       <c r="V12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <v>13.0</v>
       </c>
       <c r="W12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>1.367106e-05</v>
       </c>
       <c r="X12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>1.56e-05</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.0542478e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>7.2964901e-05</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>6.94e-05</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>8.326e-05</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1015.11</v>
+        <v>1020.357</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" s="1">
         <v>2096</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H13" t="s">
         <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J13" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K13" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L13" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M13" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K13" s="2">
+        <v>2093.0</v>
+      </c>
+      <c r="N13" s="2">
         <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L13" s="2">
+        <v>3.6684011e-05</v>
+      </c>
+      <c r="O13" s="2">
         <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>2075.0</v>
-      </c>
-      <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.6203355e-05</v>
-      </c>
-      <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.15e-05</v>
+        <v>4.186e-05</v>
       </c>
       <c r="P13" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>18.0</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>3.925665e-06</v>
+        <v>0</v>
       </c>
       <c r="R13" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>4.5e-06</v>
+        <v>0</v>
       </c>
       <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>19.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>21.0</v>
       </c>
       <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>1.9890036e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>2.208402e-05</v>
       </c>
       <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>2.28e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>2.52e-05</v>
       </c>
       <c r="V13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <v>13.0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>1.367106e-05</v>
       </c>
       <c r="X13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>1.56e-05</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.0542478e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>7.2964901e-05</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>6.94e-05</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>8.326e-05</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AD13" s="1">
-        <v>1010.229</v>
+        <v>1015.561</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD14" s="1">
-        <v>1.659</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD15" s="1">
-        <v>0.466</v>
+        <v>0.486</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>2093.0</v>
       </c>
       <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>3.65174082e-05</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>3.6684011e-05</v>
       </c>
       <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.186e-05</v>
       </c>
       <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>51.0</v>
       </c>
       <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>7.85133e-06</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>1.11734625e-05</v>
       </c>
       <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>9e-06</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>1.275e-05</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>6.281064e-06</v>
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>6.30972e-06</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V16" s="2">
@@ -3316,12 +3316,12 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>5.11732242e-05</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>5.46930035e-05</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>5.866e-05</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>6.241e-05</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3332,86 +3332,86 @@
         <v>6.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>1114.33</v>
+        <v>796.723</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F17" s="1">
-        <v>2132</v>
+        <v>2147</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>2093.0</v>
       </c>
       <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>3.65174082e-05</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>3.6684011e-05</v>
       </c>
       <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.186e-05</v>
       </c>
       <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>51.0</v>
       </c>
       <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>7.85133e-06</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>1.11734625e-05</v>
       </c>
       <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>9e-06</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>1.275e-05</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>6.281064e-06</v>
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>6.30972e-06</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V17" s="2">
@@ -3424,12 +3424,12 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>5.11732242e-05</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>5.46930035e-05</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>5.866e-05</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>6.241e-05</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3440,13 +3440,13 @@
         <v>6.0</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AD17" s="1">
-        <v>1110.728</v>
+        <v>791.888</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3501,7 +3501,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/tool_chat/report.xlsx
+++ b/reports/tool_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="160">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d143-3bb2-7940-aa9a-fce8e789c19e</t>
+    <t>01a0d587-e670-7b13-a151-5cf962dc0772</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,83 +306,83 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d143-3bbf-7260-86c0-80fcd5038b6f</t>
+    <t>01a0d587-e681-7fd0-95a0-e20fa07020cd</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    System prompt</t>
+  </si>
+  <si>
+    <t>Call echo_tool with the user's text, then answer concisely using the returned echo. The tool repeats input; it provides no independent factual evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    User prompt</t>
+  </si>
+  <si>
+    <t>Echo this text: ReAct</t>
+  </si>
+  <si>
+    <t>Cache write</t>
+  </si>
+  <si>
+    <t>Context · added / total</t>
+  </si>
+  <si>
+    <t>LLM response</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_ZU4pr7mS3q3XjEK5LMveX86H", "id": "fc_02781ffa79691b7a006ab5a3d1884887d29ecbaf6b25d75f4e", "index": 0}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_ZU4pr7mS3q3XjEK5LMveX86H", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Tool · echo_tool</t>
+  </si>
+  <si>
+    <t>01a0d587-eb9b-7512-921d-7a247e468f68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Arguments</t>
+  </si>
+  <si>
+    <t>{'text': 'ReAct'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Result</t>
+  </si>
+  <si>
+    <t>Your input was: ReAct</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0d587-eba0-7222-bfaa-77e55f585c41</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>Input at standard rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    System prompt</t>
-  </si>
-  <si>
-    <t>Call echo_tool with the user's text, then answer concisely using the returned echo. The tool repeats input; it provides no independent factual evidence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    User prompt</t>
-  </si>
-  <si>
-    <t>Echo this text: ReAct</t>
-  </si>
-  <si>
-    <t>Cache write</t>
-  </si>
-  <si>
-    <t>Context · added / total</t>
-  </si>
-  <si>
-    <t>LLM response</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_kA1D7fN7irmL7RwLmk8I9Bpq", "id": "fc_0eb7081bb50e1523006ab48c18869887d2be54906e314498bf", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_kA1D7fN7irmL7RwLmk8I9Bpq", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Tool · echo_tool</t>
-  </si>
-  <si>
-    <t>01a0d143-40d9-76c3-a8ac-560f6e865c97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Arguments</t>
-  </si>
-  <si>
-    <t>{'text': 'ReAct'}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Result</t>
-  </si>
-  <si>
-    <t>Your input was: ReAct</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d143-40de-7e43-b592-8c445294b22c</t>
-  </si>
-  <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_0eb7081bb50e1523006ab48c19675087d29493951e24343daa"}]</t>
+    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_02781ffa79691b7a006ab5a3d29d2887d2bdc9ed6b6b33ac2c"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -391,20 +391,17 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0d143-4427-79f2-9714-0f513991f047</t>
+    <t>01a0d587-f040-7640-afd7-a4a09a63ecc0</t>
   </si>
   <si>
     <t>Echo this text: Tool observations</t>
   </si>
   <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0eb7081bb50e1523006ab48c1a3fcc87d2b53434a0d7c1b0d3", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwaGso6agc0GulrjhK0U9jq7JXxfGLA4j27UZKGBFmDLXceyKl5se4I4-pJK7CMDhupaHPDh8d-h4zr1PHqiWNZ-dBSx4VJQbYHvf2RyFvcPRP4KRx-k5GrkWvw5IZdWwtgbC10-wf8PPvIW55YKDQ0SOYsApzb7jhaBTHJ0bWXpDniFLuM8KrH_NNioWX0nb-qy-g8pmDEqi-6DUzZcrCRVAKKKv_TBnapaLOJQsCf0cZaRR6ufRCyFxm2fIWEyvLZYQtH5JU2B7-rVnLukGGkADbFBFELkOeQn8kByz8nYAdq0FyXj2Ys6E6ay75TVhesOS71gyFuXY2Dge2k3XMHTDHopBxaW7ahlfzKp8pWjXE-PPXyNtv8l43SWrqfIWV8sqQEwJu8vJs8-YK-8EaqWGTKoWe4AZ_UNewiAxIlO1mGBOx4dpa5Cg9MrPT2BkT9aQwhBkd6dg_v5XlBjaTsvGiADyiFMOSwnsdRYjbLBobFRSVnv1vSttpiFxGszIi-cIKIO5C7x4Bld2saFs5aiFnZkU_i2JYvRnh21OF9eIyGSG28rEOnZ3RxuNwJP-4PLisxAmOS9byaYAVt5owdN4fpJYd-BEhhCT2DWJGHW9P_tjZo78SFl7nxi-sFUqHSK24REwxbiAgD48t9Zcvi68SomEmqzhwAkSORHmeckNx9Klwb3wqlsUh59mzl8Cq_96ekQW6EeJox7cRTjJxwhSTuShj37zfjeICmwzMZ2Wgyj8VkcRqUp4hHRfOt5yB3G17DLXaeXTixyMeWuxp7StsJ1sHl_srA0MTVS52ZE-g_1aZogaiDl1oG9nNF8L_LPEa2l19O4aiUHD3Mz-eSTmfW7cR4ICu9GhoAopz8t63IyeOl095Nfdx36jTmojl59dGrpBCFa5zq3yPYr7p-5kXwTs7P7RITtSF4GqLbNXWCG7g7XkSrhp7Kl8BZF7-Y2qwsYoU6mU8b4lKUjlkfDrj8BvFX_W3fgoBDOXlb6NK9SUSYLx0lD2E6PkmmVKz3pFMqC4XDy2aQRBNIML-InftahiXRjOElavBF0iHeCc-qZmXKhmB2pd6V9d7dNz2RIQkKlMFAxyUBy_d6EWCEc9OFaL2bJw1bFIWZZ6ZDcMNQ4w7WUXvk9KT4cS8Zw71uvBJwnFu8gURoIQ7d7os0P3eyoPL-A9UFkWB2gUPy9yZy44cpAykXXFUImRr7JjpsxRwimzgPhx-ubM_1auctvQ=="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_LeB7y3SoyKUgNjggdMJ6Dx5A", "id": "fc_0eb7081bb50e1523006ab48c1a76f487d2a56298a4b976763f", "index": 1}]
-{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_LeB7y3SoyKUgNjggdMJ6Dx5A", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d143-4822-7592-abb8-a192231f660c</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_hIGtHQlQW0UrktPNFWf625a6", "id": "fc_02781ffa79691b7a006ab5a3d4170487d296f5a74b142b30b1", "index": 0}]
+{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_hIGtHQlQW0UrktPNFWf625a6", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d587-f53f-7830-93fd-11e79e422243</t>
   </si>
   <si>
     <t>{'text': 'Tool observations'}</t>
@@ -416,10 +413,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0d143-4826-7d41-a4ee-678b4e800ed4</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_0eb7081bb50e1523006ab48c1b45f487d2bf90a9804b1e282e"}]</t>
+    <t>01a0d587-f545-79e1-979c-ca2fa2123fc4</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_02781ffa79691b7a006ab5a3d4f21c87d294b7ca2f6e7a5416"}]</t>
   </si>
   <si>
     <t>reference_chat_agent</t>
@@ -440,7 +437,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0d143-3bb5-7aa1-9449-38d127073f39</t>
+    <t>01a0d587-e674-7b92-8d77-59d9e4436359</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -452,7 +449,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d143-3bb7-7be1-ad34-30d011c64278</t>
+    <t>01a0d587-e676-7120-a065-4e2eacf408f1</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -473,7 +470,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d143-40d8-7902-9c77-d790dfc2bd1e</t>
+    <t>01a0d587-eb99-7de0-b887-fbe0b0ed935c</t>
   </si>
   <si>
     <t xml:space="preserve">        echo_tool</t>
@@ -485,22 +482,22 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0d143-40db-7542-88cb-cff6fca5b6af</t>
-  </si>
-  <si>
-    <t>01a0d143-4422-77d3-8086-047757b74f60</t>
-  </si>
-  <si>
-    <t>01a0d143-4423-7c01-b795-eba8af788806</t>
-  </si>
-  <si>
-    <t>01a0d143-4424-7793-aa4b-11ab024442cf</t>
-  </si>
-  <si>
-    <t>01a0d143-4821-7d11-a275-fa61bc1573df</t>
-  </si>
-  <si>
-    <t>01a0d143-4824-71a2-8856-10fda9df80b6</t>
+    <t>01a0d587-eb9d-7de0-91a4-3846b2cf8c2a</t>
+  </si>
+  <si>
+    <t>01a0d587-f03b-7740-b994-a71383a00a96</t>
+  </si>
+  <si>
+    <t>01a0d587-f03d-78d3-941f-e87263ad0dae</t>
+  </si>
+  <si>
+    <t>01a0d587-f03e-7990-836e-d17b55add28f</t>
+  </si>
+  <si>
+    <t>01a0d587-f53e-7182-a563-936c41cb2f6e</t>
+  </si>
+  <si>
+    <t>01a0d587-f542-7e62-9b04-0a33b933b1fe</t>
   </si>
 </sst>
 </file>
@@ -907,7 +904,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -967,20 +964,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61)=4,SUM('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.0002271061025</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0006323483146</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61)=4,SUM('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.00025915</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00071879</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>63.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -991,20 +988,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>9.9448198e-05</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
+        <v>0.0005196888102</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00011348</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
+        <v>0.00059073</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>52.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1038,23 +1035,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>2039</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5737553e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.078e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1067,27 +1064,8 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1097,8 +1075,11 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="34" customHeight="1">
+      <c r="I7" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1106,10 +1087,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1120,10 +1101,26 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2039</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000448447465</v>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>0.00050975</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>45.0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>51.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1137,32 +1134,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.0058072e-05</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="73" customHeight="1">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -1172,27 +1188,11 @@
       <c r="C13" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="5">
-        <v>19</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.998078e-05</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="73" customHeight="1">
+      <c r="I13" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1200,10 +1200,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
@@ -1217,59 +1214,59 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
-        <v>105</v>
+      <c r="C16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12)=3,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12),"Unknown")</f>
+        <v>0.000469033381</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12)=3,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12),"Unknown")</f>
+        <v>0.00053315</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>47.0</v>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>53.0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13),"Unknown")</f>
-        <v>5.6244143e-05</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13),"Unknown")</f>
-        <v>6.418e-05</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
+      <c r="M17" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="24" customHeight="1">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="C18" t="s">
         <v>113</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1">
@@ -1277,46 +1274,65 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1">
-      <c r="B20">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="C20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2078</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1">
+      <c r="A21" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2078</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" s="4" t="s">
+      <c r="C21" t="s">
         <v>119</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2039</v>
+      </c>
+      <c r="E21" s="2">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.58757972e-05</v>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C17),D21*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.078e-05</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1325,72 +1341,72 @@
         <v>97</v>
       </c>
       <c r="D22" s="5">
-        <v>2075</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6368525e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!C17),D22*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.15e-05</v>
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B17),D22*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G22" s="5">
         <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H22" s="5">
         <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="5">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="5">
-        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>120</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>117</v>
+        <v>103</v>
+      </c>
+      <c r="D24" s="5">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2">
+        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.91766e-06</v>
+      </c>
+      <c r="F24" s="2">
+        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!D17),D24*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>9e-06</v>
+      </c>
+      <c r="G24" s="5">
+        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H24" s="5">
+        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1399,34 +1415,53 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26">
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="4">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="4">
+      <c r="D26" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
+      <c r="E27" s="2">
+        <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.334128e-06</v>
+      </c>
+      <c r="F27" s="2">
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E17),D27*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="34" customHeight="1">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1434,43 +1469,24 @@
       <c r="C28" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="5">
-        <v>6</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.30972e-06</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="34" customHeight="1">
+      <c r="I28" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1479,89 +1495,108 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31">
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="4">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
-        <v>105</v>
+      <c r="C31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27)=4,SUM('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27),"Unknown")</f>
+        <v>5.06554292e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27)=4,SUM('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27),"Unknown")</f>
+        <v>5.758e-05</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="B32" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E28)=3,SUM('Turns'!E22,'Turns'!E23,'Turns'!E28),"Unknown")</f>
-        <v>4.3204055e-05</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0001126595044</v>
       </c>
       <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F28)=3,SUM('Turns'!F22,'Turns'!F23,'Turns'!F28),"Unknown")</f>
-        <v>4.93e-05</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00012806</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>111</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="B33" s="4">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" s="2">
-        <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.0001276579045</v>
-      </c>
-      <c r="F33" s="2">
-        <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.00014567</v>
-      </c>
-      <c r="G33" s="5">
-        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="H33" s="5">
-        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2096</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1">
+      <c r="A34" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="4">
-        <v>2096</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>124</v>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2075</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.650921e-05</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!C17),D34*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.15e-05</v>
+      </c>
+      <c r="G34" s="5">
+        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H34" s="5">
+        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1">
@@ -1575,23 +1610,23 @@
         <v>97</v>
       </c>
       <c r="D35" s="5">
-        <v>2093</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2">
         <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6684011e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!C17),D35*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.186e-05</v>
+        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!B17),D35*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G35" s="5">
         <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" s="5">
         <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1">
@@ -1602,26 +1637,10 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="5">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2">
-        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F36" s="2">
-        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!B17),D36*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G36" s="5">
-        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="5">
-        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>101</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
@@ -1632,10 +1651,26 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>125</v>
+        <v>103</v>
+      </c>
+      <c r="D37" s="5">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.95883e-06</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!D17),D37*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.5e-06</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
@@ -1649,32 +1684,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="24" customHeight="1">
-      <c r="A39" t="s">
+    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="4">
         <v>2</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A40" s="4" t="s">
+      <c r="D39" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="24" customHeight="1">
+      <c r="A40" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40">
         <v>2</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="4">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
+      <c r="D40" s="5">
+        <v>19</v>
+      </c>
+      <c r="E40" s="2">
+        <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.0058072e-05</v>
+      </c>
+      <c r="F40" s="2">
+        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!E17),D40*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H40" s="5">
+        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="73" customHeight="1">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -1682,26 +1736,10 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
+        <v>107</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="D41" s="5">
-        <v>13</v>
-      </c>
-      <c r="E41" s="2">
-        <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.367106e-05</v>
-      </c>
-      <c r="F41" s="2">
-        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!F17),D41*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.56e-05</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H41" s="5">
-        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
@@ -1712,29 +1750,10 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="5">
-        <v>21</v>
-      </c>
-      <c r="E42" s="2">
-        <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.208402e-05</v>
-      </c>
-      <c r="F42" s="2">
-        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E17),D42*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
-      </c>
-      <c r="G42" s="5">
-        <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H42" s="5">
-        <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="281" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="24" customHeight="1">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -1742,347 +1761,322 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
-      </c>
-      <c r="I43" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="2">
+        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40)=4,SUM('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40),"Unknown")</f>
+        <v>6.1053956e-05</v>
+      </c>
+      <c r="F44" s="2">
+        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40)=4,SUM('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40),"Unknown")</f>
+        <v>6.94e-05</v>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H44" s="5">
+        <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B45" s="4">
+        <v>2</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M45" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="24" customHeight="1">
-      <c r="A44" t="s">
-        <v>123</v>
-      </c>
-      <c r="B44">
+    <row r="46" spans="1:13" ht="24" customHeight="1">
+      <c r="B46">
         <v>2</v>
       </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="24" customHeight="1">
-      <c r="A45" t="s">
-        <v>123</v>
-      </c>
-      <c r="B45">
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24" customHeight="1">
+      <c r="B47">
         <v>2</v>
       </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B46" s="4">
+      <c r="C47" t="s">
+        <v>115</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="4">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42)=4,SUM('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42),"Unknown")</f>
-        <v>7.2964901e-05</v>
-      </c>
-      <c r="F46" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42)=4,SUM('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42),"Unknown")</f>
-        <v>8.326e-05</v>
-      </c>
-      <c r="G46" s="5">
-        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H46" s="5">
-        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B47" s="4">
-        <v>2</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="24" customHeight="1">
-      <c r="B48">
-        <v>2</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="24" customHeight="1">
+      <c r="C48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2132</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="24" customHeight="1">
+      <c r="A49" t="s">
+        <v>130</v>
+      </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
-      </c>
-      <c r="I49" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2093</v>
+      </c>
+      <c r="E49" s="2">
+        <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.68259164e-05</v>
+      </c>
+      <c r="F49" s="2">
+        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C17),D49*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.186e-05</v>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="24" customHeight="1">
+      <c r="A50" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>2</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" s="4">
-        <v>2147</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="24" customHeight="1">
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="5">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2">
+        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="F50" s="2">
+        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G50" s="5">
+        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H50" s="5">
+        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="5">
-        <v>2093</v>
-      </c>
-      <c r="E51" s="2">
-        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6684011e-05</v>
-      </c>
-      <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="G51" s="5">
-        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H51" s="5">
-        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24" customHeight="1">
+        <v>120</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D52" s="5">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E52" s="2">
         <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>7.91766e-06</v>
       </c>
       <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!D17),D52*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>9e-06</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="24" customHeight="1">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
-      </c>
-      <c r="I53" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A54" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="24" customHeight="1">
-      <c r="A54" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54">
+      <c r="B54" s="4">
         <v>2</v>
       </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="5">
-        <v>51</v>
-      </c>
-      <c r="E54" s="2">
-        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.11734625e-05</v>
-      </c>
-      <c r="F54" s="2">
-        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.275e-05</v>
-      </c>
-      <c r="G54" s="5">
-        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H54" s="5">
-        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="24" customHeight="1">
+      <c r="C54" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="24" customHeight="1">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="4">
+        <v>106</v>
+      </c>
+      <c r="D55" s="5">
+        <v>6</v>
+      </c>
+      <c r="E55" s="2">
+        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.334128e-06</v>
+      </c>
+      <c r="F55" s="2">
+        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G55" s="5">
+        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H55" s="5">
+        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="34" customHeight="1">
+      <c r="A56" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56">
         <v>2</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="24" customHeight="1">
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" s="5">
-        <v>6</v>
-      </c>
-      <c r="E57" s="2">
-        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.30972e-06</v>
-      </c>
-      <c r="F57" s="2">
-        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="G57" s="5">
-        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H57" s="5">
-        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="34" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="24" customHeight="1">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
-      <c r="A59" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="4">
         <v>2</v>
       </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="24" customHeight="1">
-      <c r="A60" t="s">
-        <v>131</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A61" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" s="4">
-        <v>2</v>
-      </c>
-      <c r="C61" s="4" t="s">
+      <c r="C59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="2">
+        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55)=4,SUM('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55),"Unknown")</f>
+        <v>5.16055484e-05</v>
+      </c>
+      <c r="F59" s="2">
+        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55)=4,SUM('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55),"Unknown")</f>
+        <v>5.866e-05</v>
+      </c>
+      <c r="G59" s="5">
+        <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H59" s="5">
+        <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K59" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E61" s="2">
-        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57)=4,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57),"Unknown")</f>
-        <v>5.46930035e-05</v>
-      </c>
-      <c r="F61" s="2">
-        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57)=4,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57),"Unknown")</f>
-        <v>6.241e-05</v>
-      </c>
-      <c r="G61" s="5">
-        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H61" s="5">
-        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>111</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE61">
+  <conditionalFormatting sqref="A2:AE59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2203,69 +2197,72 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D23)=2,SUM('Turns'!D6,'Turns'!D23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D22)=2,SUM('Turns'!D5,'Turns'!D22),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E23)=2,SUM('Turns'!E6,'Turns'!E23),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E22)=2,SUM('Turns'!E5,'Turns'!E22),"Unknown")</f>
+        <v>1.055688e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F23)=2,SUM('Turns'!F6,'Turns'!F23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F22)=2,SUM('Turns'!F5,'Turns'!F22),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D22)=2,SUM('Turns'!D5,'Turns'!D22),"Unknown")</f>
-        <v>4114.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>2039.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E22)=2,SUM('Turns'!E5,'Turns'!E22),"Unknown")</f>
-        <v>7.2106078e-05</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.58757972e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F22)=2,SUM('Turns'!F5,'Turns'!F22),"Unknown")</f>
-        <v>8.228e-05</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>4.078e-05</v>
       </c>
       <c r="P2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D9,'Turns'!D24)=2,SUM('Turns'!D9,'Turns'!D24),"Unknown")</f>
+        <v>2075.0</v>
       </c>
       <c r="Q2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9,'Turns'!E24)=2,SUM('Turns'!E9,'Turns'!E24),"Unknown")</f>
+        <v>0.000456365125</v>
       </c>
       <c r="R2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9,'Turns'!F24)=2,SUM('Turns'!F9,'Turns'!F24),"Unknown")</f>
+        <v>0.00051875</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D27)=2,SUM('Turns'!D12,'Turns'!D27),"Unknown")</f>
         <v>25.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>2.62905e-05</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E27)=2,SUM('Turns'!E12,'Turns'!E27),"Unknown")</f>
+        <v>2.63922e-05</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F27)=2,SUM('Turns'!F12,'Turns'!F27),"Unknown")</f>
         <v>3e-05</v>
       </c>
       <c r="V2" s="2">
@@ -2278,128 +2275,128 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>9.9448198e-05</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
+        <v>0.0005196888102</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00011348</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
+        <v>0.00059073</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>52.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>59.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2137.39</v>
+        <v>2468.391</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" t="s">
         <v>139</v>
-      </c>
-      <c r="H3" t="s">
-        <v>140</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.497</v>
+        <v>0.526</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" t="s">
         <v>143</v>
-      </c>
-      <c r="H4" t="s">
-        <v>144</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2039.0</v>
       </c>
-      <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.5737553e-05</v>
-      </c>
-      <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.078e-05</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000448447465</v>
       </c>
       <c r="R4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00050975</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
         <v>19.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>1.998078e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>2.28e-05</v>
       </c>
       <c r="V4" s="2">
@@ -2412,99 +2409,99 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>5.6244143e-05</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000469033381</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>6.418e-05</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.00053315</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>53.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1312.13</v>
+        <v>1313.574</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1">
         <v>2042</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2039.0</v>
       </c>
-      <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.5737553e-05</v>
-      </c>
-      <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.078e-05</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
       <c r="Q5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000448447465</v>
       </c>
       <c r="R5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00050975</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
         <v>19.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>1.998078e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>2.28e-05</v>
       </c>
       <c r="V5" s="2">
@@ -2517,163 +2514,166 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>5.6244143e-05</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000469033381</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>6.418e-05</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.00053315</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>53.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1301.829</v>
+        <v>1301.444</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" t="s">
         <v>150</v>
-      </c>
-      <c r="H6" t="s">
-        <v>151</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>2.268</v>
+        <v>2.626</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.59</v>
+        <v>0.663</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2075.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>2039.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>3.6368525e-05</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.58757972e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.15e-05</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>4.078e-05</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
+        <v>7.91766e-06</v>
       </c>
       <c r="R8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>6.30972e-06</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.334128e-06</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V8" s="2">
@@ -2686,99 +2686,102 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>4.3204055e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>5.06554292e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>4.93e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>5.758e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>817.1180000000001</v>
+        <v>1144.149</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="1">
         <v>2078</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2075.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>2039.0</v>
       </c>
       <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>3.6368525e-05</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.58757972e-05</v>
       </c>
       <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.15e-05</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>4.078e-05</v>
       </c>
       <c r="P9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
+        <v>7.91766e-06</v>
       </c>
       <c r="R9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>6.30972e-06</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.334128e-06</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V9" s="2">
@@ -2791,519 +2794,516 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>4.3204055e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>5.06554292e-05</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>4.93e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>5.758e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AD9" s="1">
-        <v>812.37</v>
+        <v>1138.829</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D36,'Turns'!D52)=2,SUM('Turns'!D36,'Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35,'Turns'!D50)=2,SUM('Turns'!D35,'Turns'!D50),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E36,'Turns'!E52)=2,SUM('Turns'!E36,'Turns'!E52),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
+        <v>1.055688e-06</v>
       </c>
       <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F36,'Turns'!F52)=2,SUM('Turns'!F36,'Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M10" s="2">
-        <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
-        <v>4186.0</v>
+        <f>IF(COUNT('Turns'!D34,'Turns'!D49)=2,SUM('Turns'!D34,'Turns'!D49),"Unknown")</f>
+        <v>4168.0</v>
       </c>
       <c r="N10" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E51)=2,SUM('Turns'!E35,'Turns'!E51),"Unknown")</f>
-        <v>7.3368022e-05</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>7.33351264e-05</v>
       </c>
       <c r="O10" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F51)=2,SUM('Turns'!F35,'Turns'!F51),"Unknown")</f>
-        <v>8.372e-05</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>8.336e-05</v>
       </c>
       <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>51.0</v>
+        <f>IF(COUNT('Turns'!D37,'Turns'!D52)=2,SUM('Turns'!D37,'Turns'!D52),"Unknown")</f>
+        <v>54.0</v>
       </c>
       <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>1.11734625e-05</v>
+        <f>IF(COUNT('Turns'!E37,'Turns'!E52)=2,SUM('Turns'!E37,'Turns'!E52),"Unknown")</f>
+        <v>1.187649e-05</v>
       </c>
       <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>1.275e-05</v>
+        <f>IF(COUNT('Turns'!F37,'Turns'!F52)=2,SUM('Turns'!F37,'Turns'!F52),"Unknown")</f>
+        <v>1.35e-05</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D42,'Turns'!D57)=2,SUM('Turns'!D42,'Turns'!D57),"Unknown")</f>
-        <v>27.0</v>
+        <f>IF(COUNT('Turns'!D40,'Turns'!D55)=2,SUM('Turns'!D40,'Turns'!D55),"Unknown")</f>
+        <v>25.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
-        <v>2.839374e-05</v>
+        <f>IF(COUNT('Turns'!E40,'Turns'!E55)=2,SUM('Turns'!E40,'Turns'!E55),"Unknown")</f>
+        <v>2.63922e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
-        <v>3.24e-05</v>
+        <f>IF(COUNT('Turns'!F40,'Turns'!F55)=2,SUM('Turns'!F40,'Turns'!F55),"Unknown")</f>
+        <v>3e-05</v>
       </c>
       <c r="V10" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>13.0</v>
+        <v>0</v>
       </c>
       <c r="W10" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.367106e-05</v>
+        <v>0</v>
       </c>
       <c r="X10" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>1.56e-05</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.0001276579045</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0001126595044</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.00014567</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00012806</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>1824.015</v>
+        <v>2135.619</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.348</v>
+        <v>0.488</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J12" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K12" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L12" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>2093.0</v>
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>2075.0</v>
       </c>
       <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>3.6684011e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>3.650921e-05</v>
       </c>
       <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>4.186e-05</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>4.15e-05</v>
       </c>
       <c r="P12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>18.0</v>
       </c>
       <c r="Q12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>3.95883e-06</v>
       </c>
       <c r="R12" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>4.5e-06</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>2.208402e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V12" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>13.0</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.367106e-05</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>1.56e-05</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>7.2964901e-05</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>6.1053956e-05</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>8.326e-05</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>6.94e-05</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1020.357</v>
+        <v>1278.844</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F13" s="1">
         <v>2096</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H13" t="s">
         <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J13" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K13" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L13" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>2093.0</v>
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>2075.0</v>
       </c>
       <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>3.6684011e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>3.650921e-05</v>
       </c>
       <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>4.186e-05</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>4.15e-05</v>
       </c>
       <c r="P13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>18.0</v>
       </c>
       <c r="Q13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>3.95883e-06</v>
       </c>
       <c r="R13" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>4.5e-06</v>
       </c>
       <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>2.208402e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V13" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>13.0</v>
+        <v>0</v>
       </c>
       <c r="W13" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.367106e-05</v>
+        <v>0</v>
       </c>
       <c r="X13" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>1.56e-05</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>7.2964901e-05</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>6.1053956e-05</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>8.326e-05</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>6.94e-05</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AD13" s="1">
-        <v>1015.561</v>
+        <v>1274.675</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AD14" s="1">
-        <v>1.73</v>
+        <v>2.755</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD15" s="1">
-        <v>0.486</v>
+        <v>0.791</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J16" s="2">
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K16" s="2">
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L16" s="2">
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M16" s="2">
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>2093.0</v>
+      </c>
+      <c r="N16" s="2">
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>3.68259164e-05</v>
+      </c>
+      <c r="O16" s="2">
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>4.186e-05</v>
+      </c>
+      <c r="P16" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K16" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="Q16" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L16" s="2">
+        <v>7.91766e-06</v>
+      </c>
+      <c r="R16" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2093.0</v>
-      </c>
-      <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>3.6684011e-05</v>
-      </c>
-      <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>51.0</v>
-      </c>
-      <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>1.11734625e-05</v>
-      </c>
-      <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>1.275e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>6.30972e-06</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>6.334128e-06</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V16" s="2">
@@ -3316,12 +3316,12 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>5.46930035e-05</v>
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>5.16055484e-05</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>6.241e-05</v>
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>5.866e-05</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3332,86 +3332,86 @@
         <v>6.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>796.723</v>
+        <v>847.422</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="1">
-        <v>2147</v>
+        <v>2132</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J17" s="2">
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K17" s="2">
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L17" s="2">
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M17" s="2">
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>2093.0</v>
+      </c>
+      <c r="N17" s="2">
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>3.68259164e-05</v>
+      </c>
+      <c r="O17" s="2">
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>4.186e-05</v>
+      </c>
+      <c r="P17" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K17" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="Q17" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L17" s="2">
+        <v>7.91766e-06</v>
+      </c>
+      <c r="R17" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2093.0</v>
-      </c>
-      <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>3.6684011e-05</v>
-      </c>
-      <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>51.0</v>
-      </c>
-      <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>1.11734625e-05</v>
-      </c>
-      <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>1.275e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>6.30972e-06</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>6.334128e-06</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
         <v>7.2e-06</v>
       </c>
       <c r="V17" s="2">
@@ -3424,12 +3424,12 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>5.46930035e-05</v>
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>5.16055484e-05</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>6.241e-05</v>
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>5.866e-05</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3440,13 +3440,13 @@
         <v>6.0</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD17" s="1">
-        <v>791.888</v>
+        <v>842.297</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3501,7 +3501,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/tool_chat/report.xlsx
+++ b/reports/tool_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="187">
   <si>
     <t>Request</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d587-e670-7b13-a151-5cf962dc0772</t>
+    <t>01a1143f-6441-7a22-a31c-1a1915e9a0ff</t>
   </si>
   <si>
     <t>Recording</t>
   </si>
   <si>
-    <t>Provider trace</t>
+    <t>Offline simulation</t>
   </si>
   <si>
     <t>FX reference date</t>
@@ -216,7 +216,7 @@
     <t>Pricing scope</t>
   </si>
   <si>
-    <t>Standard online token rates. Verify rates and model access before use. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. No batch, regional, long-context, tool, or negotiated pricing adjustments are applied.</t>
+    <t>Published online token rates verified 2026-10-05. Copilot uses GitHub rates, including saved long-context tiers, before plan allowances; these are usage estimates, not subscription invoices. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. Direct OpenAI and Anthropic entries use standard rates; no batch, regional, tool, negotiated, or unrecorded context-tier adjustments are applied. Model availability and context capacity require separate verification.</t>
   </si>
   <si>
     <t>Model</t>
@@ -252,7 +252,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>https://developers.openai.com/api/docs/models/gpt-5.5.md</t>
@@ -291,6 +291,99 @@
     <t>Illustrative demo rates based on openai:gpt-5.6-luna; no provider billing</t>
   </si>
   <si>
+    <t>anthropic:claude-haiku-4-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-haiku-4-5-20251001</t>
+  </si>
+  <si>
+    <t>anthropic:claude-opus-5-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-4-6</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-5-5</t>
+  </si>
+  <si>
+    <t>copilot:claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t>https://docs.github.com/en/copilot/reference/copilot-billing/models-and-pricing</t>
+  </si>
+  <si>
+    <t>copilot:claude-opus-5.5</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-5.5</t>
+  </si>
+  <si>
+    <t>copilot:gemini-3.8-flash</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-astra.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-luna.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-sol.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6.1-sol.md</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4 [long context]</t>
+  </si>
+  <si>
+    <t>Above 272,000 input tokens</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol [long context]</t>
+  </si>
+  <si>
     <t>Run total</t>
   </si>
   <si>
@@ -303,10 +396,10 @@
     <t>LLM request</t>
   </si>
   <si>
-    <t>gpt-5.6-luna</t>
-  </si>
-  <si>
-    <t>01a0d587-e681-7fd0-95a0-e20fa07020cd</t>
+    <t>scripted-chat</t>
+  </si>
+  <si>
+    <t>01a1143f-6444-7680-bc85-0a90355e7da8</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -342,8 +435,7 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_ZU4pr7mS3q3XjEK5LMveX86H", "id": "fc_02781ffa79691b7a006ab5a3d1884887d29ecbaf6b25d75f4e", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_ZU4pr7mS3q3XjEK5LMveX86H", "type": "tool_call"}</t>
+    <t>{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "reference-1", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,7 +447,7 @@
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0d587-eb9b-7512-921d-7a247e468f68</t>
+    <t>01a1143f-64c5-7f82-947a-0ca5a458daaa</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -373,7 +465,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d587-eba0-7222-bfaa-77e55f585c41</t>
+    <t>01a1143f-64c7-7432-b7e2-cd7cb402eabb</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -382,7 +474,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "ReAct", "phase": "final_answer", "index": 0, "id": "msg_02781ffa79691b7a006ab5a3d29d2887d2bdc9ed6b6b33ac2c"}]</t>
+    <t>The tool returned "Your input was: ReAct". This shows the model requesting a tool and then reading its result.</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -391,17 +483,17 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0d587-f040-7640-afd7-a4a09a63ecc0</t>
+    <t>01a1143f-64da-79b2-bb70-8cfdd71325cd</t>
   </si>
   <si>
     <t>Echo this text: Tool observations</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"Tool observations\"}", "call_id": "call_hIGtHQlQW0UrktPNFWf625a6", "id": "fc_02781ffa79691b7a006ab5a3d4170487d296f5a74b142b30b1", "index": 0}]
-{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "call_hIGtHQlQW0UrktPNFWf625a6", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d587-f53f-7830-93fd-11e79e422243</t>
+    <t>I will echo the text through the local tool.
+{"name": "echo_tool", "args": {"text": "Tool observations"}, "id": "reference-2", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a1143f-64de-70a2-beb0-52f17b493c75</t>
   </si>
   <si>
     <t>{'text': 'Tool observations'}</t>
@@ -413,10 +505,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0d587-f545-79e1-979c-ca2fa2123fc4</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Tool observations", "phase": "final_answer", "index": 0, "id": "msg_02781ffa79691b7a006ab5a3d4f21c87d294b7ca2f6e7a5416"}]</t>
+    <t>01a1143f-64e0-74e3-a5b3-78238b132705</t>
+  </si>
+  <si>
+    <t>The tool returned "Your input was: Tool observations". The next model request includes that result. This echo repeats supplied text and adds no independent evidence.</t>
   </si>
   <si>
     <t>reference_chat_agent</t>
@@ -431,48 +523,39 @@
     <t>Subtree total</t>
   </si>
   <si>
-    <t xml:space="preserve">    PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>Check message history and repair missing tool responses before the agent starts.</t>
-  </si>
-  <si>
-    <t>01a0d587-e674-7b92-8d77-59d9e4436359</t>
+    <t xml:space="preserve">    model</t>
+  </si>
+  <si>
+    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
+  </si>
+  <si>
+    <t>01a1143f-6443-7f50-b6a4-980bd9cd6c47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SimulatedModel</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>Watch an agent echo your input through a tool.</t>
+  </si>
+  <si>
+    <t>Own call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    tools</t>
+  </si>
+  <si>
+    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
+  </si>
+  <si>
+    <t>01a1143f-64c5-7f82-947a-0c90945e3935</t>
   </si>
   <si>
     <t>No model charge</t>
   </si>
   <si>
-    <t xml:space="preserve">    model</t>
-  </si>
-  <si>
-    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
-  </si>
-  <si>
-    <t>01a0d587-e676-7120-a065-4e2eacf408f1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ChatOpenAI</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>Generate the next assistant message or tool request from the current conversation.</t>
-  </si>
-  <si>
-    <t>Own call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    tools</t>
-  </si>
-  <si>
-    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
-  </si>
-  <si>
-    <t>01a0d587-eb99-7de0-b887-fbe0b0ed935c</t>
-  </si>
-  <si>
     <t xml:space="preserve">        echo_tool</t>
   </si>
   <si>
@@ -482,22 +565,19 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0d587-eb9d-7de0-91a4-3846b2cf8c2a</t>
-  </si>
-  <si>
-    <t>01a0d587-f03b-7740-b994-a71383a00a96</t>
-  </si>
-  <si>
-    <t>01a0d587-f03d-78d3-941f-e87263ad0dae</t>
-  </si>
-  <si>
-    <t>01a0d587-f03e-7990-836e-d17b55add28f</t>
-  </si>
-  <si>
-    <t>01a0d587-f53e-7182-a563-936c41cb2f6e</t>
-  </si>
-  <si>
-    <t>01a0d587-f542-7e62-9b04-0a33b933b1fe</t>
+    <t>01a1143f-64c7-7432-b7e2-cd69558c2618</t>
+  </si>
+  <si>
+    <t>01a1143f-64d9-71c0-9d6a-90e1dab89467</t>
+  </si>
+  <si>
+    <t>01a1143f-64da-79b2-bb70-8ce531e628e5</t>
+  </si>
+  <si>
+    <t>01a1143f-64dd-7ff3-8cc9-d0daa1018b93</t>
+  </si>
+  <si>
+    <t>01a1143f-64df-7832-b9ec-d82145a6dff0</t>
   </si>
 </sst>
 </file>
@@ -961,23 +1041,23 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0006323483146</v>
+        <v>0.0002935516432</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00071879</v>
+        <v>0.00033368</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>63.0</v>
+        <v>29.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>72.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -985,263 +1065,271 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005196888102</v>
+        <v>0.0001457905128</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059073</v>
+        <v>0.00016572</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>15.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4">
-        <v>2042</v>
+        <v>162</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>2.8503576e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B22),D5*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>3.24e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>129</v>
+      </c>
+      <c r="D6" s="1">
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>130</v>
+      </c>
+      <c r="D7" s="1">
+        <v>53</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="1">
+        <v>30</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2039</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000448447465</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00050975</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>134</v>
+      </c>
+      <c r="D9" s="1">
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D10" s="1">
+        <v>162</v>
+      </c>
+      <c r="L10" s="1">
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D11" s="4">
-        <v>19</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D12" s="5">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.0058072e-05</v>
+        <v>5.7007152e-05</v>
       </c>
       <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E22),D12*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.48e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="73" customHeight="1">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="34" customHeight="1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="D14" s="1">
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D15" s="1">
+        <v>54</v>
+      </c>
+      <c r="L15" s="1">
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12)=3,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12),"Unknown")</f>
-        <v>0.000469033381</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
+        <v>8.5510728e-05</v>
       </c>
       <c r="F16" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12)=3,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12),"Unknown")</f>
-        <v>0.00053315</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
+        <v>9.72e-05</v>
       </c>
       <c r="G16" s="5">
         <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>9.0</v>
       </c>
       <c r="H16" s="5">
         <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>10.0</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1249,13 +1337,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1">
@@ -1263,10 +1351,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1">
@@ -1274,255 +1362,257 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D20" s="4">
-        <v>2078</v>
+        <v>249</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D21" s="5">
-        <v>2039</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.58757972e-05</v>
+        <v>3.8004768e-06</v>
       </c>
       <c r="F21" s="2">
-        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C17),D21*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.078e-05</v>
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C22),D21*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>4.32e-06</v>
       </c>
       <c r="G21" s="5">
         <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H21" s="5">
         <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D22" s="5">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>5.806284e-06</v>
       </c>
       <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B17),D22*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B22),D22*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>6.6e-06</v>
       </c>
       <c r="G22" s="5">
         <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="5">
         <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>151</v>
+      </c>
+      <c r="D23" s="1">
+        <v>33</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="5">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2">
-        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.91766e-06</v>
-      </c>
-      <c r="F24" s="2">
-        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!D17),D24*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>9e-06</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="5">
-        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D25" s="1">
+        <v>33</v>
+      </c>
+      <c r="L25" s="1">
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B26" s="4">
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D26" s="4">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D27" s="5">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.334128e-06</v>
+        <v>5.0673024e-05</v>
       </c>
       <c r="F27" s="2">
-        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E17),D27*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E22),D27*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>5.76e-05</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H27" s="5">
         <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="34" customHeight="1">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="D29" s="1">
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D30" s="1">
+        <v>48</v>
+      </c>
+      <c r="L30" s="1">
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B31" s="4">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="E31" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27)=4,SUM('Turns'!E21,'Turns'!E22,'Turns'!E24,'Turns'!E27),"Unknown")</f>
-        <v>5.06554292e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E27)=3,SUM('Turns'!E21,'Turns'!E22,'Turns'!E27),"Unknown")</f>
+        <v>6.02797848e-05</v>
       </c>
       <c r="F31" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27)=4,SUM('Turns'!F21,'Turns'!F22,'Turns'!F24,'Turns'!F27),"Unknown")</f>
-        <v>5.758e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F27)=3,SUM('Turns'!F21,'Turns'!F22,'Turns'!F27),"Unknown")</f>
+        <v>6.852e-05</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1530,268 +1620,270 @@
         <v>2</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="E32" s="2">
         <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0001126595044</v>
+        <v>0.0001477611304</v>
       </c>
       <c r="F32" s="2">
         <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00012806</v>
+        <v>0.00016796</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B33" s="4">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D33" s="4">
-        <v>2096</v>
+        <v>327</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D34" s="5">
-        <v>2075</v>
+        <v>297</v>
       </c>
       <c r="E34" s="2">
         <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.650921e-05</v>
+        <v>5.2256556e-06</v>
       </c>
       <c r="F34" s="2">
-        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!C17),D34*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.15e-05</v>
+        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!C22),D34*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>5.94e-06</v>
       </c>
       <c r="G34" s="5">
         <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H34" s="5">
         <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D35" s="5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2">
         <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>5.27844e-06</v>
       </c>
       <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!B17),D35*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!B22),D35*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>6e-06</v>
       </c>
       <c r="G35" s="5">
         <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H35" s="5">
         <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="D36" s="1">
+        <v>30</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="5">
-        <v>18</v>
-      </c>
-      <c r="E37" s="2">
-        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.95883e-06</v>
-      </c>
-      <c r="F37" s="2">
-        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!D17),D37*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.5e-06</v>
-      </c>
-      <c r="G37" s="5">
-        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="5">
-        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>134</v>
+      </c>
+      <c r="D37" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D38" s="1">
+        <v>30</v>
+      </c>
+      <c r="L38" s="1">
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B39" s="4">
         <v>2</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D39" s="4">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D40" s="5">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2">
         <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.0058072e-05</v>
+        <v>6.7564032e-05</v>
       </c>
       <c r="F40" s="2">
-        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!E17),D40*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
+        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!E22),D40*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>7.68e-05</v>
       </c>
       <c r="G40" s="5">
         <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H40" s="5">
         <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="73" customHeight="1">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="47" customHeight="1">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="D42" s="1">
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="24" customHeight="1">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D43" s="1">
+        <v>64</v>
+      </c>
+      <c r="L43" s="1">
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B44" s="4">
         <v>2</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40)=4,SUM('Turns'!E34,'Turns'!E35,'Turns'!E37,'Turns'!E40),"Unknown")</f>
-        <v>6.1053956e-05</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E35,'Turns'!E40)=3,SUM('Turns'!E34,'Turns'!E35,'Turns'!E40),"Unknown")</f>
+        <v>7.80681276e-05</v>
       </c>
       <c r="F44" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40)=4,SUM('Turns'!F34,'Turns'!F35,'Turns'!F37,'Turns'!F40),"Unknown")</f>
-        <v>6.94e-05</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F35,'Turns'!F40)=3,SUM('Turns'!F34,'Turns'!F35,'Turns'!F40),"Unknown")</f>
+        <v>8.874e-05</v>
       </c>
       <c r="G44" s="5">
         <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H44" s="5">
         <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1799,13 +1891,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="24" customHeight="1">
@@ -1813,10 +1905,10 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="24" customHeight="1">
@@ -1824,255 +1916,257 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B48" s="4">
         <v>2</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D48" s="4">
-        <v>2132</v>
+        <v>424</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="24" customHeight="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="24" customHeight="1">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D49" s="5">
-        <v>2093</v>
+        <v>391</v>
       </c>
       <c r="E49" s="2">
         <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.68259164e-05</v>
+        <v>6.8795668e-06</v>
       </c>
       <c r="F49" s="2">
-        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C17),D49*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.186e-05</v>
+        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C22),D49*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>7.82e-06</v>
       </c>
       <c r="G49" s="5">
         <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H49" s="5">
         <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="24" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="24" customHeight="1">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D50" s="5">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E50" s="2">
         <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>5.806284e-06</v>
       </c>
       <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B22),D50*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>6.6e-06</v>
       </c>
       <c r="G50" s="5">
         <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H50" s="5">
         <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="24" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>151</v>
+      </c>
+      <c r="D51" s="1">
+        <v>33</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="24" customHeight="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" s="5">
-        <v>36</v>
-      </c>
-      <c r="E52" s="2">
-        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.91766e-06</v>
-      </c>
-      <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!D17),D52*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>9e-06</v>
-      </c>
-      <c r="G52" s="5">
-        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H52" s="5">
-        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="24" customHeight="1">
+        <v>134</v>
+      </c>
+      <c r="D52" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="24" customHeight="1">
       <c r="A53" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D53" s="1">
+        <v>33</v>
+      </c>
+      <c r="L53" s="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B54" s="4">
         <v>2</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D54" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="24" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="24" customHeight="1">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D55" s="5">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E55" s="2">
         <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.334128e-06</v>
+        <v>5.7007152e-05</v>
       </c>
       <c r="F55" s="2">
-        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-06</v>
+        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E22),D55*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.48e-05</v>
       </c>
       <c r="G55" s="5">
         <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H55" s="5">
         <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="34" customHeight="1">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="34" customHeight="1">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="24" customHeight="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="24" customHeight="1">
+        <v>134</v>
+      </c>
+      <c r="D57" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="24" customHeight="1">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D58" s="1">
+        <v>54</v>
+      </c>
+      <c r="L58" s="1">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B59" s="4">
         <v>2</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2">
-        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55)=4,SUM('Turns'!E49,'Turns'!E50,'Turns'!E52,'Turns'!E55),"Unknown")</f>
-        <v>5.16055484e-05</v>
+        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E55)=3,SUM('Turns'!E49,'Turns'!E50,'Turns'!E55),"Unknown")</f>
+        <v>6.96930028e-05</v>
       </c>
       <c r="F59" s="2">
-        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55)=4,SUM('Turns'!F49,'Turns'!F50,'Turns'!F52,'Turns'!F55),"Unknown")</f>
-        <v>5.866e-05</v>
+        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F55)=3,SUM('Turns'!F49,'Turns'!F50,'Turns'!F55),"Unknown")</f>
+        <v>7.922e-05</v>
       </c>
       <c r="G59" s="5">
         <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="H59" s="5">
         <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2184,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -2197,73 +2291,70 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D22)=2,SUM('Turns'!D5,'Turns'!D22),"Unknown")</f>
-        <v>6.0</v>
+        <v>195.0</v>
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E22)=2,SUM('Turns'!E5,'Turns'!E22),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <v>3.430986e-05</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F22)=2,SUM('Turns'!F5,'Turns'!F22),"Unknown")</f>
-        <v>1.2e-06</v>
+        <v>3.9e-05</v>
       </c>
       <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
+        <v>216.0</v>
       </c>
       <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.58757972e-05</v>
+        <v>3.8004768e-06</v>
       </c>
       <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <v>4.32e-06</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D24)=2,SUM('Turns'!D9,'Turns'!D24),"Unknown")</f>
-        <v>2075.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E24)=2,SUM('Turns'!E9,'Turns'!E24),"Unknown")</f>
-        <v>0.000456365125</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F24)=2,SUM('Turns'!F9,'Turns'!F24),"Unknown")</f>
-        <v>0.00051875</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D27)=2,SUM('Turns'!D12,'Turns'!D27),"Unknown")</f>
-        <v>25.0</v>
+        <v>102.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E27)=2,SUM('Turns'!E12,'Turns'!E27),"Unknown")</f>
-        <v>2.63922e-05</v>
+        <v>0.000107680176</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F27)=2,SUM('Turns'!F12,'Turns'!F27),"Unknown")</f>
-        <v>3e-05</v>
+        <v>0.0001224</v>
       </c>
       <c r="V2" s="2">
         <v>0</v>
@@ -2276,95 +2367,165 @@
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
-        <v>0.0005196888102</v>
+        <v>0.0001457905128</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
-        <v>0.00059073</v>
+        <v>0.00016572</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2468.391</v>
+        <v>136.06</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
+      <c r="J3" s="2">
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>162.0</v>
+      </c>
+      <c r="K3" s="2">
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>2.8503576e-05</v>
+      </c>
+      <c r="L3" s="2">
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>3.24e-05</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>54.0</v>
+      </c>
+      <c r="T3" s="2">
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>5.7007152e-05</v>
+      </c>
+      <c r="U3" s="2">
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.48e-05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>8.5510728e-05</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>9.72e-05</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
       <c r="AD3" s="1">
-        <v>0.526</v>
+        <v>128.865</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>110</v>
+      <c r="F4" s="1">
+        <v>162</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="H4" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="J4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
+        <v>162.0</v>
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>2.8503576e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
+        <v>3.24e-05</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -2376,28 +2537,25 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2039.0</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000448447465</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00050975</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>19.0</v>
+        <v>54.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.0058072e-05</v>
+        <v>5.7007152e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.28e-05</v>
+        <v>6.48e-05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -2410,271 +2568,268 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000469033381</v>
+        <v>8.5510728e-05</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.00053315</v>
+        <v>9.72e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>10.0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AD4" s="1">
-        <v>1313.574</v>
+        <v>127.304</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2042</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="I5" t="s">
-        <v>143</v>
-      </c>
-      <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2039.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000448447465</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00050975</v>
-      </c>
-      <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-      <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000469033381</v>
-      </c>
-      <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.00053315</v>
-      </c>
-      <c r="AA5" s="5">
-        <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="AB5" s="5">
-        <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>1301.444</v>
+        <v>1.396</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="AD6" s="1">
-        <v>2.626</v>
+        <v>0.434</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
+        <v>49</v>
+      </c>
+      <c r="J7" s="2">
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>5.806284e-06</v>
+      </c>
+      <c r="L7" s="2">
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>6.6e-06</v>
+      </c>
+      <c r="M7" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>216.0</v>
+      </c>
+      <c r="N7" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.8004768e-06</v>
+      </c>
+      <c r="O7" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>4.32e-06</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="T7" s="2">
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>5.0673024e-05</v>
+      </c>
+      <c r="U7" s="2">
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>5.76e-05</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>6.02797848e-05</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>6.852e-05</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.663</v>
+        <v>2.809</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>110</v>
+      <c r="F8" s="1">
+        <v>249</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="H8" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>3.0</v>
+        <v>33.0</v>
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>5.806284e-06</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>6e-07</v>
+        <v>6.6e-06</v>
       </c>
       <c r="M8" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
+        <v>216.0</v>
       </c>
       <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.58757972e-05</v>
+        <v>3.8004768e-06</v>
       </c>
       <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <v>4.32e-06</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>7.91766e-06</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>6.0</v>
+        <v>48.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>6.334128e-06</v>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>7.2e-06</v>
+        <v>5.76e-05</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2687,102 +2842,96 @@
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.06554292e-05</v>
+        <v>6.02797848e-05</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.758e-05</v>
+        <v>6.852e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="AD8" s="1">
-        <v>1144.149</v>
+        <v>1.317</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B9" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2078</v>
+        <v>141</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I9" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D35,'Turns'!D50)=2,SUM('Turns'!D35,'Turns'!D50),"Unknown")</f>
+        <v>63.0</v>
       </c>
       <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
+        <v>1.1084724e-05</v>
       </c>
       <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
+        <v>1.26e-05</v>
       </c>
       <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>2039.0</v>
+        <f>IF(COUNT('Turns'!D34,'Turns'!D49)=2,SUM('Turns'!D34,'Turns'!D49),"Unknown")</f>
+        <v>688.0</v>
       </c>
       <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.58757972e-05</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>1.21052224e-05</v>
       </c>
       <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>4.078e-05</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>1.376e-05</v>
       </c>
       <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>7.91766e-06</v>
+        <v>0</v>
       </c>
       <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D40,'Turns'!D55)=2,SUM('Turns'!D40,'Turns'!D55),"Unknown")</f>
+        <v>118.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>6.334128e-06</v>
+        <f>IF(COUNT('Turns'!E40,'Turns'!E55)=2,SUM('Turns'!E40,'Turns'!E55),"Unknown")</f>
+        <v>0.000124571184</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>7.2e-06</v>
+        <f>IF(COUNT('Turns'!F40,'Turns'!F55)=2,SUM('Turns'!F40,'Turns'!F55),"Unknown")</f>
+        <v>0.0001416</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2794,100 +2943,97 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>5.06554292e-05</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
+        <v>0.0001477611304</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.758e-05</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
+        <v>0.00016796</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>117</v>
+        <v>17.0</v>
       </c>
       <c r="AD9" s="1">
-        <v>1138.829</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="H10" t="s">
-        <v>155</v>
+        <v>184</v>
+      </c>
+      <c r="I10" t="s">
+        <v>183</v>
       </c>
       <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D35,'Turns'!D50)=2,SUM('Turns'!D35,'Turns'!D50),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
+        <v>30.0</v>
       </c>
       <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>5.27844e-06</v>
       </c>
       <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
+        <v>6e-06</v>
       </c>
       <c r="M10" s="2">
-        <f>IF(COUNT('Turns'!D34,'Turns'!D49)=2,SUM('Turns'!D34,'Turns'!D49),"Unknown")</f>
-        <v>4168.0</v>
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>297.0</v>
       </c>
       <c r="N10" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
-        <v>7.33351264e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>5.2256556e-06</v>
       </c>
       <c r="O10" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
-        <v>8.336e-05</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>5.94e-06</v>
       </c>
       <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D37,'Turns'!D52)=2,SUM('Turns'!D37,'Turns'!D52),"Unknown")</f>
-        <v>54.0</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E37,'Turns'!E52)=2,SUM('Turns'!E37,'Turns'!E52),"Unknown")</f>
-        <v>1.187649e-05</v>
+        <v>0</v>
       </c>
       <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F37,'Turns'!F52)=2,SUM('Turns'!F37,'Turns'!F52),"Unknown")</f>
-        <v>1.35e-05</v>
+        <v>0</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D40,'Turns'!D55)=2,SUM('Turns'!D40,'Turns'!D55),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>64.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E40,'Turns'!E55)=2,SUM('Turns'!E40,'Turns'!E55),"Unknown")</f>
-        <v>2.63922e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>6.7564032e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F40,'Turns'!F55)=2,SUM('Turns'!F40,'Turns'!F55),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>7.68e-05</v>
       </c>
       <c r="V10" s="2">
         <v>0</v>
@@ -2899,558 +3045,412 @@
         <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>0.0001126595044</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>7.80681276e-05</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>0.00012806</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>8.874e-05</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>2135.619</v>
+        <v>2.803</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
+      </c>
+      <c r="F11" s="1">
+        <v>327</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="H11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I11" t="s">
-        <v>155</v>
+        <v>184</v>
+      </c>
+      <c r="J11" s="2">
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
+        <v>30.0</v>
+      </c>
+      <c r="K11" s="2">
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>5.27844e-06</v>
+      </c>
+      <c r="L11" s="2">
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
+        <v>6e-06</v>
+      </c>
+      <c r="M11" s="2">
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>297.0</v>
+      </c>
+      <c r="N11" s="2">
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>5.2256556e-06</v>
+      </c>
+      <c r="O11" s="2">
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>5.94e-06</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>64.0</v>
+      </c>
+      <c r="T11" s="2">
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>6.7564032e-05</v>
+      </c>
+      <c r="U11" s="2">
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>7.68e-05</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>7.80681276e-05</v>
+      </c>
+      <c r="Z11" s="2">
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>8.874e-05</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.488</v>
+        <v>1.916</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K12" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L12" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>2075.0</v>
-      </c>
-      <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.650921e-05</v>
-      </c>
-      <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.15e-05</v>
-      </c>
-      <c r="P12" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="Q12" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>3.95883e-06</v>
-      </c>
-      <c r="R12" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>4.5e-06</v>
-      </c>
-      <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-      <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="V12" s="2">
-        <v>0</v>
-      </c>
-      <c r="W12" s="2">
-        <v>0</v>
-      </c>
-      <c r="X12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.1053956e-05</v>
-      </c>
-      <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>6.94e-05</v>
-      </c>
-      <c r="AA12" s="5">
-        <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="AB12" s="5">
-        <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>183</v>
       </c>
       <c r="AD12" s="1">
-        <v>1278.844</v>
+        <v>1.366</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2096</v>
+        <v>141</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
-      </c>
-      <c r="J13" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K13" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L13" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>2075.0</v>
-      </c>
-      <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.650921e-05</v>
-      </c>
-      <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.15e-05</v>
-      </c>
-      <c r="P13" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="Q13" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
-        <v>3.95883e-06</v>
-      </c>
-      <c r="R13" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
-        <v>4.5e-06</v>
-      </c>
-      <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-      <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2">
-        <v>0</v>
-      </c>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.1053956e-05</v>
-      </c>
-      <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>6.94e-05</v>
-      </c>
-      <c r="AA13" s="5">
-        <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="AB13" s="5">
-        <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="AD13" s="1">
-        <v>1274.675</v>
+        <v>0.419</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>183</v>
+      </c>
+      <c r="J14" s="2">
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="K14" s="2">
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>5.806284e-06</v>
+      </c>
+      <c r="L14" s="2">
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>6.6e-06</v>
+      </c>
+      <c r="M14" s="2">
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>391.0</v>
+      </c>
+      <c r="N14" s="2">
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.8795668e-06</v>
+      </c>
+      <c r="O14" s="2">
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.82e-06</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>54.0</v>
+      </c>
+      <c r="T14" s="2">
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>5.7007152e-05</v>
+      </c>
+      <c r="U14" s="2">
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>6.48e-05</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>6.96930028e-05</v>
+      </c>
+      <c r="Z14" s="2">
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>7.922e-05</v>
+      </c>
+      <c r="AA14" s="5">
+        <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="AB14" s="5">
+        <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>2.755</v>
+        <v>2.023</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
+      </c>
+      <c r="F15" s="1">
+        <v>424</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="H15" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>186</v>
+      </c>
+      <c r="J15" s="2">
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="K15" s="2">
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>5.806284e-06</v>
+      </c>
+      <c r="L15" s="2">
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>6.6e-06</v>
+      </c>
+      <c r="M15" s="2">
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>391.0</v>
+      </c>
+      <c r="N15" s="2">
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.8795668e-06</v>
+      </c>
+      <c r="O15" s="2">
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.82e-06</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>54.0</v>
+      </c>
+      <c r="T15" s="2">
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>5.7007152e-05</v>
+      </c>
+      <c r="U15" s="2">
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>6.48e-05</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>6.96930028e-05</v>
+      </c>
+      <c r="Z15" s="2">
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>7.922e-05</v>
+      </c>
+      <c r="AA15" s="5">
+        <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="AB15" s="5">
+        <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="AD15" s="1">
-        <v>0.791</v>
+        <v>1.265</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="54" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H16" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" t="s">
-        <v>155</v>
-      </c>
-      <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
-        <v>2093.0</v>
-      </c>
-      <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>3.68259164e-05</v>
-      </c>
-      <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>36.0</v>
-      </c>
-      <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>7.91766e-06</v>
-      </c>
-      <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>9e-06</v>
-      </c>
-      <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>6.334128e-06</v>
-      </c>
-      <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="V16" s="2">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>5.16055484e-05</v>
-      </c>
-      <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>5.866e-05</v>
-      </c>
-      <c r="AA16" s="5">
-        <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="AB16" s="5">
-        <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>847.422</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="54" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2132</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H17" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" t="s">
-        <v>159</v>
-      </c>
-      <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
-        <v>2093.0</v>
-      </c>
-      <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>3.68259164e-05</v>
-      </c>
-      <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
-        <v>4.186e-05</v>
-      </c>
-      <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>36.0</v>
-      </c>
-      <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>7.91766e-06</v>
-      </c>
-      <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>9e-06</v>
-      </c>
-      <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>6.334128e-06</v>
-      </c>
-      <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>7.2e-06</v>
-      </c>
-      <c r="V17" s="2">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>5.16055484e-05</v>
-      </c>
-      <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>5.866e-05</v>
-      </c>
-      <c r="AA17" s="5">
-        <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="AB17" s="5">
-        <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>842.297</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE17">
+  <conditionalFormatting sqref="A2:AE15">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -3464,7 +3464,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -3849,6 +3849,731 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.00</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.075</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="F33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="72" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="72" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E39" s="2">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="72" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="72" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="72" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="F43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="72" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="D44" s="2">
+        <v>25.00</v>
+      </c>
+      <c r="E44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="F44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="72" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.40</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
